--- a/output/第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx
+++ b/output/第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx
@@ -66,7 +66,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -91,11 +91,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -135,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -154,9 +149,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -166,14 +158,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
@@ -184,10 +176,10 @@
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -598,7 +590,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>出所</t>
+          <t>出所（すべて年報・令和7年度）</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -623,17 +615,17 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告（年報・令和7年度）の要介護認定者数</t>
+          <t>様式1の5(12) 要介護（要支援）認定者数（年度末・第1号被保険者）</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>要介護度別の実数（01シート）</t>
+          <t>要介護度別の実数（01シート）。性別・年齢階級別も年報にあり必要に応じて出せる</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>確定値。当方が保有している</t>
+          <t>確定値</t>
         </is>
       </c>
     </row>
@@ -648,17 +640,17 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>見える化システム 総括表詳細（１）の令和7年度（年間の延べ人月）÷12</t>
+          <t>様式1の7(16)(18)（現物給付分の受給者数）及び様式1の6(15)（施設介護サービス受給者数）÷12</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>サービス別の月平均と要介護度別の内訳（02シート）</t>
+          <t>サービス別・要介護度別の月平均（02シート）</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>サービス計は確定値。要介護度別は按分による推定値</t>
+          <t>確定値</t>
         </is>
       </c>
     </row>
@@ -673,17 +665,17 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>様式1の7(16)(18)÷12。特定福祉用具購入費・住宅改修費は現物給付がないため様式2の件数÷12</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>サービス別の月平均と要介護度別の内訳（03シート）</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>同上</t>
+          <t>サービス別・要介護度別の月平均（03シート）</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>確定値</t>
         </is>
       </c>
     </row>
@@ -698,25 +690,26 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>総括表詳細（３）の1人1月あたり利用回（日）数×③の利用者数</t>
+          <t>様式1の7(17)(19)（現物給付分の利用回（日）数）÷12</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>サービス別の要支援計・要介護計（04シート）</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>要支援・要介護の2区分まで。要介護度別には分けられない</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>注1）当方が先にお示ししたのは②③の2画面だけでした。①を差し替えないと利用率の分母が令和8年度のままになり、利用者数だけを令和7年度に置いても令和7年度の利用率になりません。他の保険者の同種の作業（弊社の別案件）では4画面をすべて差し替えており、その方法を参照しました。数値は当広域連合のデータから算定しており、借用していません。
-注2）年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2の要介護度別のデータをご提供いただければ、②③④も確定値にできます（確認事項No.134）。</t>
+          <t>サービス別・要介護度別の月平均（04シート）</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>確定値</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>注1）当方が先にお示ししたのは②③の2画面だけでした。①を差し替えないと利用率の分母が令和8年度のままになり、利用者数だけを令和7年度に置いても令和7年度の利用率になりません。
+注2）令和8年9月11日に年報（令和7年度）の全様式を電子データで確認したことにより、②③④の要介護度別の内訳が按分による推定値ではなく確定値になりました（それ以前は在宅サービス利用率による按分でした）。要介護度別に合計して12で除した値が見える化システムの総括表詳細（１）の令和7年度と全サービスで一致することを06シートで検算しています。
+注3）年報は令和8年8月28日に受領済みの資料（資料No.22）と同一のものです。当方は主要値のみを取り込んでおり、サービス種別×要介護度の明細を取り込んでいませんでした。確認事項No.134は当方の取込漏れによるものであり、取り下げます。</t>
         </is>
       </c>
     </row>
@@ -748,12 +741,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>画面の値と総括表の月平均が食い違う</t>
+          <t>画面の値と年報の月平均が食い違う</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度は整数である。特定施設入居者生活介護は画面64人に対し総括表61.50人（＋4.1％）、介護老人保健施設は画面130人に対し総括表134.08人（▲3.0％）。総括表は給付費の合計が年報と円単位で一致する系列であり、こちらを用いる（05シート）</t>
+          <t>画面の令和7年度は整数である。特定施設入居者生活介護は画面64人に対し年報61.50人（＋4.1％）、介護老人保健施設は画面130人に対し年報134.08人（▲3.0％）、介護医療院は画面6人に対し年報5.50人（＋9.1％）。本表は年報の値を用いる（05シート）</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr"/>
@@ -828,7 +821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -915,59 +908,339 @@
           <t>認定者数（人）</t>
         </is>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="9" t="n">
         <v>298</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="9" t="n">
         <v>292</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="9" t="n">
         <v>515</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F5" s="9" t="n">
         <v>299</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="9" t="n">
         <v>212</v>
       </c>
-      <c r="H5" s="10" t="n">
+      <c r="H5" s="9" t="n">
         <v>213</v>
       </c>
-      <c r="I5" s="10" t="n">
+      <c r="I5" s="9" t="n">
         <v>155</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="11" t="inlineStr"/>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr"/>
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr"/>
-      <c r="D6" s="11" t="inlineStr"/>
-      <c r="E6" s="11" t="inlineStr"/>
-      <c r="F6" s="11" t="inlineStr"/>
-      <c r="G6" s="11" t="inlineStr"/>
-      <c r="H6" s="11" t="inlineStr"/>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr"/>
+      <c r="D6" s="10" t="inlineStr"/>
+      <c r="E6" s="10" t="inlineStr"/>
+      <c r="F6" s="10" t="inlineStr"/>
+      <c r="G6" s="10" t="inlineStr"/>
+      <c r="H6" s="10" t="inlineStr"/>
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>第1号被保険者 1,984人（要支援 590人・要介護 1,394人）。第2号被保険者 36人</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>（参考）年齢階級別の内訳　第1号被保険者・男女計</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="4" t="inlineStr"/>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>年齢階級</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>要支援1</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>要支援2</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>要介護1</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>要介護2</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>要介護3</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>要介護4</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>要介護5</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="6" t="inlineStr"/>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>65歳以上70歳未満</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="6" t="inlineStr"/>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>70歳以上75歳未満</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="6" t="inlineStr"/>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>75歳以上80歳未満</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="6" t="inlineStr"/>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>80歳以上85歳未満</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="6" t="inlineStr"/>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>85歳以上90歳未満</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="6" t="inlineStr"/>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>90歳以上</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="10" t="inlineStr"/>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>298</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>292</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>515</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>299</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>212</v>
+      </c>
+      <c r="H16" s="11" t="n">
+        <v>213</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>155</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>注1）★の行が入力値です。
-注2）見える化システムの画面が性別・年齢階級別の入力を求める場合は、当方はその内訳を保有していないため用意できません。年報（様式1の5）のご提供をお願いします（確認事項No.134）。
+注2）画面が性別・年齢階級別の入力を求める場合は、年齢階級別は上表のとおりです。性別は男 602人・女 1,382人で、年齢階級との組合せも年報（様式1の5）にあります。
 注3）総括表の要介護認定者数1,943人は令和7年9月末時点であり、本表の1,984人（令和8年3月末）とは時点が異なります。推計の実績値として置くのは年度末の値です。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A18:I18"/>
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
@@ -1007,7 +1280,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>総括表詳細（１）の令和7年度（年間の延べ人月）を12で除した。サービス計は確定値。要介護度別の内訳は画面の令和7年度の構成比による按分であり推定値である。上段が小数、下段が整数（最大剰余法で群の合計を保つ）。</t>
+          <t>年報（令和7年度）の様式1の7(16)(18)及び様式1の6(15)の要介護度別の年間の延べ人数を12で除した。すべて確定値である。上段が小数、下段が整数（最大剰余法で群の合計を保つ）。</t>
         </is>
       </c>
     </row>
@@ -1084,25 +1357,25 @@
         <v>61.5</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>7.81</v>
+        <v>8</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>5.857</v>
+        <v>5.333</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>14.643</v>
+        <v>14.917</v>
       </c>
       <c r="H5" s="12" t="n">
-        <v>7.81</v>
+        <v>8</v>
       </c>
       <c r="I5" s="12" t="n">
-        <v>7.81</v>
+        <v>8.167</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>10.738</v>
+        <v>10.75</v>
       </c>
       <c r="K5" s="12" t="n">
-        <v>6.833</v>
+        <v>6.333</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -1120,10 +1393,10 @@
         <v>8</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H6" s="13" t="n">
         <v>8</v>
@@ -1135,7 +1408,7 @@
         <v>11</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -1157,28 +1430,26 @@
       <c r="D7" s="12" t="n">
         <v>81.583</v>
       </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="E7" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>0.995</v>
+        <v>0.417</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>10.944</v>
+        <v>12</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>18.903</v>
+        <v>18.667</v>
       </c>
       <c r="I7" s="12" t="n">
-        <v>21.888</v>
+        <v>21.75</v>
       </c>
       <c r="J7" s="12" t="n">
-        <v>14.924</v>
+        <v>15</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>13.929</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -1192,19 +1463,17 @@
       <c r="D8" s="13" t="n">
         <v>82</v>
       </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="E8" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I8" s="13" t="n">
         <v>22</v>
@@ -1235,15 +1504,11 @@
       <c r="D9" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="E9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="G9" s="12" t="n">
         <v>0</v>
@@ -1272,15 +1537,11 @@
       <c r="D10" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="E10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>0</v>
@@ -1317,30 +1578,26 @@
       <c r="D11" s="12" t="n">
         <v>59.25</v>
       </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="E11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1.975</v>
+        <v>2.167</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>11.85</v>
+        <v>10.667</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>9.875</v>
+        <v>10.167</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>20.738</v>
+        <v>21.417</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>14.813</v>
+        <v>14.833</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -1354,27 +1611,23 @@
       <c r="D12" s="13" t="n">
         <v>59</v>
       </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="E12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>2</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I12" s="13" t="n">
         <v>10</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K12" s="13" t="n">
         <v>15</v>
@@ -1399,30 +1652,26 @@
       <c r="D13" s="12" t="n">
         <v>138.25</v>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="E13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>6.863</v>
+        <v>5.75</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>17.649</v>
+        <v>18.333</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>42.161</v>
+        <v>43</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>46.083</v>
+        <v>46.333</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>25.493</v>
+        <v>24.833</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -1436,24 +1685,20 @@
       <c r="D14" s="13" t="n">
         <v>138</v>
       </c>
-      <c r="E14" s="14" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="E14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H14" s="13" t="n">
         <v>18</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J14" s="13" t="n">
         <v>46</v>
@@ -1481,30 +1726,26 @@
       <c r="D15" s="12" t="n">
         <v>134.083</v>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="E15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>29.911</v>
+        <v>30.5</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>34.037</v>
+        <v>30.917</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>25.785</v>
+        <v>25.5</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>31.974</v>
+        <v>33.167</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>12.377</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -1518,30 +1759,26 @@
       <c r="D16" s="13" t="n">
         <v>134</v>
       </c>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="F16" s="14" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="E16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I16" s="13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J16" s="13" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K16" s="13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1563,15 +1800,11 @@
       <c r="D17" s="12" t="n">
         <v>5.5</v>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="E17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>0</v>
@@ -1583,10 +1816,10 @@
         <v>0</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>5.5</v>
+        <v>5.417</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -1600,15 +1833,11 @@
       <c r="D18" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="E18" s="14" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="F18" s="14" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="E18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="G18" s="13" t="n">
         <v>0</v>
@@ -1627,31 +1856,45 @@
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="11" t="inlineStr"/>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr"/>
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr"/>
-      <c r="D19" s="15" t="n">
+      <c r="C19" s="10" t="inlineStr"/>
+      <c r="D19" s="14" t="n">
         <v>480.167</v>
       </c>
-      <c r="E19" s="11" t="inlineStr"/>
-      <c r="F19" s="11" t="inlineStr"/>
-      <c r="G19" s="11" t="inlineStr"/>
-      <c r="H19" s="11" t="inlineStr"/>
-      <c r="I19" s="11" t="inlineStr"/>
-      <c r="J19" s="11" t="inlineStr"/>
-      <c r="K19" s="11" t="inlineStr"/>
+      <c r="E19" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <v>65.333</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>86.583</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>108.583</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>126.75</v>
+      </c>
+      <c r="K19" s="14" t="n">
+        <v>79.167</v>
+      </c>
     </row>
     <row r="21" ht="56" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>注1）★の行（小数）が入力値です。入力欄が整数しか受け付けない場合は下段の整数を用います。
 注2）施設・居住系の計は480.167人です。画面の令和8年度（4か月）は474人、画面の令和7年度は482人です。
-注3）地域密着型特定施設入居者生活介護は区域内に事業所がなく0です。
-注4）要介護度別の内訳は推定値です。年報（様式1の6・様式1の7）のご提供により確定値にできます。</t>
+注3）地域密着型特定施設入居者生活介護は区域内に事業所がなく0です。認知症対応型共同生活介護と特定施設入居者生活介護は短期利用の欄が年報にありますが、いずれも実績は0です。
+注4）施設サービス（特養・老健・介護医療院）は第2号被保険者を含みます。第2号は介護老人保健施設に15人（年間の延べ人数）のみです。</t>
         </is>
       </c>
     </row>
@@ -1696,14 +1939,14 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>総括表詳細（１）の令和7年度（年間の延べ人月）を12で除した。サービス計は確定値。要介護度別の内訳は、在宅サービス利用率（令和7年度・要介護度別）に在宅の認定者数を乗じた重みによる按分であり推定値である。</t>
+          <t>年報（令和7年度）の様式1の7(16)(18)の要介護度別の年間の延べ人数を12で除した。すべて確定値である。特定福祉用具購入費・住宅改修費は現物給付がないため様式2の件数による（総括表も同じ）。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　在宅の認定者数（按分の分母）</t>
+          <t>1　在宅の認定者数（画面の利用率の分母）</t>
         </is>
       </c>
     </row>
@@ -1794,29 +2037,29 @@
           <t>施設・居住系の利用者数</t>
         </is>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="15" t="n">
         <v>480.167</v>
       </c>
-      <c r="D7" s="16" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>6.852</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>64.336</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>90.248</v>
-      </c>
-      <c r="H7" s="16" t="n">
-        <v>107.519</v>
-      </c>
-      <c r="I7" s="16" t="n">
-        <v>124.456</v>
-      </c>
-      <c r="J7" s="16" t="n">
-        <v>78.94499999999999</v>
+      <c r="D7" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>65.333</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>86.583</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>108.583</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>126.75</v>
+      </c>
+      <c r="J7" s="15" t="n">
+        <v>79.167</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -1826,35 +2069,35 @@
           <t>在宅の認定者数（差引き）</t>
         </is>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="16" t="n">
         <v>1503.833</v>
       </c>
-      <c r="D8" s="17" t="n">
-        <v>290.19</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>285.148</v>
-      </c>
-      <c r="F8" s="17" t="n">
-        <v>450.664</v>
-      </c>
-      <c r="G8" s="17" t="n">
-        <v>208.752</v>
-      </c>
-      <c r="H8" s="17" t="n">
-        <v>104.481</v>
-      </c>
-      <c r="I8" s="17" t="n">
-        <v>88.544</v>
-      </c>
-      <c r="J8" s="17" t="n">
-        <v>76.05500000000001</v>
+      <c r="D8" s="16" t="n">
+        <v>290</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>286.25</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>449.667</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>212.417</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>103.417</v>
+      </c>
+      <c r="I8" s="16" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="J8" s="16" t="n">
+        <v>75.833</v>
       </c>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>注1）在宅サービス利用率の分母は在宅の認定者数です。素案の令和8年度の値を同年度の利用率で割ると50人以上のサービスでいずれも1,500人前後になり、分母が共通であることを確かめています。</t>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>注1）本表の入力値は年報の実数であり、この分母を用いた按分によるものではありません。上表は、画面に表示される在宅サービス利用率（利用者数÷在宅の認定者数）を読むために掲げています。素案の令和8年度の値を同年度の利用率で割ると50人以上のサービスでいずれも1,500人前後になり、分母が共通であることを確かめています。</t>
         </is>
       </c>
     </row>
@@ -1927,30 +2170,26 @@
       <c r="C14" s="12" t="n">
         <v>270.083</v>
       </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="D14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>104.277</v>
+        <v>99.917</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>46.894</v>
+        <v>49.667</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>42.788</v>
+        <v>42.583</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>41.403</v>
+        <v>44.417</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>34.722</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -1963,30 +2202,26 @@
       <c r="C15" s="13" t="n">
         <v>270</v>
       </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="D15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="13" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H15" s="13" t="n">
         <v>43</v>
       </c>
       <c r="I15" s="13" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -2010,19 +2245,19 @@
         <v>0</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>1.694</v>
+        <v>1.167</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.277</v>
+        <v>0.25</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>1.126</v>
+        <v>1.167</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>2.153</v>
+        <v>2.417</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2042,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" s="13" t="n">
         <v>0</v>
@@ -2054,7 +2289,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -2072,25 +2307,25 @@
         <v>135.167</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>11.112</v>
+        <v>10.25</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>14.923</v>
+        <v>14.167</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>42.299</v>
+        <v>41.083</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>22.673</v>
+        <v>25.417</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>14.24</v>
+        <v>13.833</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>14.09</v>
+        <v>15.167</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>15.829</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2104,25 +2339,25 @@
         <v>135</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F19" s="13" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H19" s="13" t="n">
         <v>14</v>
       </c>
       <c r="I19" s="13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J19" s="13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -2140,25 +2375,25 @@
         <v>66.917</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>4.277</v>
+        <v>3.167</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>9.484</v>
+        <v>10.333</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>20.662</v>
+        <v>20.25</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>16.429</v>
+        <v>16.833</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>8.768000000000001</v>
+        <v>7.833</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>2.728</v>
+        <v>3.833</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>4.569</v>
+        <v>4.667</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2172,22 +2407,22 @@
         <v>67</v>
       </c>
       <c r="D21" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I21" s="13" t="n">
         <v>4</v>
-      </c>
-      <c r="E21" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="F21" s="13" t="n">
-        <v>21</v>
-      </c>
-      <c r="G21" s="13" t="n">
-        <v>16</v>
-      </c>
-      <c r="H21" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="I21" s="13" t="n">
-        <v>3</v>
       </c>
       <c r="J21" s="13" t="n">
         <v>4</v>
@@ -2208,25 +2443,25 @@
         <v>193.25</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>7.896</v>
+        <v>7</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>7.759</v>
+        <v>7</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>37.253</v>
+        <v>37.5</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>30.984</v>
+        <v>31.083</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>36.518</v>
+        <v>37.5</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>38.285</v>
+        <v>39.833</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>34.555</v>
+        <v>33.333</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2240,13 +2475,13 @@
         <v>193</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F23" s="13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G23" s="13" t="n">
         <v>31</v>
@@ -2255,10 +2490,10 @@
         <v>37</v>
       </c>
       <c r="I23" s="13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J23" s="13" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -2275,30 +2510,26 @@
       <c r="C24" s="12" t="n">
         <v>97.333</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="D24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>52.907</v>
+        <v>49.667</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>19.117</v>
+        <v>22.083</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>11.054</v>
+        <v>10.75</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>11.065</v>
+        <v>11.667</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>3.191</v>
+        <v>3.167</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2311,27 +2542,23 @@
       <c r="C25" s="13" t="n">
         <v>97</v>
       </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E25" s="14" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="D25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H25" s="13" t="n">
         <v>11</v>
       </c>
       <c r="I25" s="13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J25" s="13" t="n">
         <v>3</v>
@@ -2352,25 +2579,25 @@
         <v>273.25</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>32.784</v>
+        <v>31.167</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>51.072</v>
+        <v>52.25</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>100.615</v>
+        <v>97.75</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>48.765</v>
+        <v>51.917</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>19.669</v>
+        <v>20</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>13.402</v>
+        <v>13.5</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>6.943</v>
+        <v>6.667</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2384,16 +2611,16 @@
         <v>273</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H27" s="13" t="n">
         <v>20</v>
@@ -2420,25 +2647,25 @@
         <v>26.5</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>0.57</v>
+        <v>0.583</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>0.853</v>
+        <v>0.917</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>6.024</v>
+        <v>6.417</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>11.142</v>
+        <v>10.417</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>3.545</v>
+        <v>3.417</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>3.079</v>
+        <v>3.5</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>1.287</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2452,22 +2679,22 @@
         <v>26</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="13" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H29" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" s="13" t="n">
         <v>4</v>
-      </c>
-      <c r="I29" s="13" t="n">
-        <v>3</v>
       </c>
       <c r="J29" s="13" t="n">
         <v>1</v>
@@ -2488,25 +2715,25 @@
         <v>16.583</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>0.734</v>
+        <v>0.417</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>4.063</v>
+        <v>2.833</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>3.925</v>
+        <v>5.167</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>3.17</v>
+        <v>2.75</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>3.621</v>
+        <v>4.167</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>1.07</v>
+        <v>1.167</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2526,10 +2753,10 @@
         <v>0</v>
       </c>
       <c r="F31" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H31" s="13" t="n">
         <v>3</v>
@@ -2556,25 +2783,25 @@
         <v>642.083</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>71.929</v>
+        <v>66.25</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>119.368</v>
+        <v>118.75</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>180.725</v>
+        <v>177.5</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>119.069</v>
+        <v>123</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>64.274</v>
+        <v>65.917</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>45.707</v>
+        <v>49.667</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>41.012</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -2588,22 +2815,22 @@
         <v>642</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E33" s="13" t="n">
         <v>119</v>
       </c>
       <c r="F33" s="13" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="H33" s="13" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I33" s="13" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J33" s="13" t="n">
         <v>41</v>
@@ -2624,25 +2851,25 @@
         <v>10.75</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>0.5580000000000001</v>
+        <v>1.667</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>2.063</v>
+        <v>2.083</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>4.706</v>
+        <v>3.5</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>2.294</v>
+        <v>2.167</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>0.833</v>
+        <v>0.667</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>0.219</v>
+        <v>0.5</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>0.077</v>
+        <v>0.167</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2656,13 +2883,13 @@
         <v>11</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" s="13" t="n">
         <v>2</v>
       </c>
       <c r="F35" s="13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G35" s="13" t="n">
         <v>2</v>
@@ -2692,25 +2919,25 @@
         <v>8.417</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>2.275</v>
+        <v>2.25</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>1.743</v>
+        <v>1.583</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>1.767</v>
+        <v>2.333</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.746</v>
+        <v>1.25</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>1.518</v>
+        <v>0.583</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>0.184</v>
+        <v>0.167</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>0.184</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -2730,7 +2957,7 @@
         <v>2</v>
       </c>
       <c r="F37" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G37" s="13" t="n">
         <v>1</v>
@@ -2760,25 +2987,25 @@
         <v>913.333</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>107.317</v>
+        <v>100.25</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>154.969</v>
+        <v>156.667</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>305.502</v>
+        <v>298.583</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>159.928</v>
+        <v>167.583</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>77.28700000000001</v>
+        <v>77.25</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>62.263</v>
+        <v>67.333</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>46.067</v>
+        <v>45.667</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -2792,22 +3019,22 @@
         <v>913</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F39" s="13" t="n">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="H39" s="13" t="n">
         <v>77</v>
       </c>
       <c r="I39" s="13" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J39" s="13" t="n">
         <v>46</v>
@@ -2827,30 +3054,26 @@
       <c r="C40" s="12" t="n">
         <v>0.583</v>
       </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="D40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>0.283</v>
+        <v>0.25</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.131</v>
+        <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>0.066</v>
+        <v>0</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>0.056</v>
+        <v>0</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>0.048</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -2863,30 +3086,26 @@
       <c r="C41" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="14" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E41" s="14" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="D41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="F41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="13" t="n">
         <v>1</v>
-      </c>
-      <c r="G41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="13" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -2903,30 +3122,26 @@
       <c r="C42" s="12" t="n">
         <v>76.167</v>
       </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="D42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>37.444</v>
+        <v>37.083</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>23.251</v>
+        <v>23.583</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>8.597</v>
+        <v>8.667</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>3.616</v>
+        <v>3.833</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>3.259</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -2939,15 +3154,11 @@
       <c r="C43" s="13" t="n">
         <v>76</v>
       </c>
-      <c r="D43" s="14" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E43" s="14" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="D43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="F43" s="13" t="n">
         <v>37</v>
@@ -3048,25 +3259,25 @@
         <v>99.917</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>4.84</v>
+        <v>4.167</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>9.510999999999999</v>
+        <v>9.333</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>38.728</v>
+        <v>37.75</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>21.462</v>
+        <v>23.083</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>16.727</v>
+        <v>17.167</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>2.919</v>
+        <v>3.333</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>5.73</v>
+        <v>5.083</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3080,16 +3291,16 @@
         <v>100</v>
       </c>
       <c r="D47" s="13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E47" s="13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F47" s="13" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H47" s="13" t="n">
         <v>17</v>
@@ -3098,16 +3309,16 @@
         <v>3</v>
       </c>
       <c r="J47" s="13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" ht="56" customHeight="1">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>注2）★の行（小数）が入力値です。
-注3）整数に丸めると0又は1になるサービスが2件あります（定期巡回・随時対応型訪問介護看護・認知症対応型通所介護）。0を入れると令和9年度から令和11年度も0のまま残るため、小数で入力できるかをご確認ください。
-注4）区域内に事業所がなく実績もないサービス（夜間対応型訪問介護・看護小規模多機能型居宅介護・短期入所療養介護（病院等）・短期入所療養介護（介護医療院）・登録施設介護支援）は総括表に行がないため本表に載せていません。画面にある場合は0を入れます。
-注5）定期巡回・随時対応型訪問介護看護は、画面の利用率が要介護1から要介護5まですべて0.0％と表示されます。利用率は0.1％刻み（在宅の認定者数約1,500人に対し約1.5人）であり、月平均0.583人はこの刻みに満たないためです。按分の重みが作れないので、在宅の認定者数そのもので割り振りました。要介護度別の内訳は推定にとどまります（確認事項No.134）。</t>
+注3）整数に丸めると0又は1になるサービスが2件あります（定期巡回・随時対応型訪問介護看護・認知症対応型通所介護）。0を入れると令和9年度から令和11年度も0のまま残るため、小数で入力できるかをご確認ください。定期巡回・随時対応型訪問介護看護は要介護1が3人・要介護5が4人（いずれも年間の延べ人数）で、整数に丸めると要介護1が0、要介護5が0となります。
+注4）区域内に事業所がなく実績もないサービス（夜間対応型訪問介護・看護小規模多機能型居宅介護・短期入所療養介護（病院等）・短期入所療養介護（介護医療院）・登録施設介護支援）は年報の値が0であるため本表に載せていません。画面にある場合は0を入れます。
+注5）要支援の欄が0のサービスが6件あります（訪問介護・訪問入浴介護・通所介護・定期巡回・随時対応型訪問介護看護・地域密着型通所介護・認知症対応型通所介護）。予防給付が総合事業へ移行したもの（訪問介護・通所介護）と、予防給付の区分がないもの（地域密着型通所介護）です。</t>
         </is>
       </c>
     </row>
@@ -3130,17 +3341,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -3153,7 +3367,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>総括表詳細（３）の1人1月あたり利用回（日）数に③の利用者数を乗じたもの。総括表詳細（３）は要支援・要介護の2区分であるため、要介護度別には分けられない。</t>
+          <t>年報（令和7年度）の様式1の7(17)(19)の要介護度別の年間の延べ回（日）数を12で除した。すべて確定値である。画面が要支援・要介護の2区分しか持たない場合は、下段の2区分の計を用いる。</t>
         </is>
       </c>
     </row>
@@ -3166,35 +3380,47 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>1人1月あたり
-要支援</t>
+          <t>単位</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>同 要介護</t>
+          <t>サービス計</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>利用者数
-要支援計</t>
+          <t>要支援1</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>同 要介護計</t>
+          <t>要支援2</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>利用回（日）数
-要支援計</t>
+          <t>要介護1</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>同 要介護計</t>
+          <t>要介護2</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>要介護3</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>要介護4</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>要介護5</t>
         </is>
       </c>
     </row>
@@ -3211,56 +3437,56 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="D5" s="18" t="n">
-        <v>55.41</v>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>270.083</v>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>14965.083</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0</v>
+        <v>2356.75</v>
       </c>
       <c r="H5" s="12" t="n">
+        <v>1815</v>
+      </c>
+      <c r="I5" s="12" t="n">
+        <v>2880.167</v>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>4122.5</v>
+      </c>
+      <c r="K5" s="12" t="n">
+        <v>3790.667</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>（2区分）</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr"/>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="15" t="n">
         <v>14965.083</v>
       </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>訪問入浴介護</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="12" t="n">
-        <v>33</v>
-      </c>
+      <c r="E6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="17" t="n">
+        <v>14965.083</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+      <c r="K6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
@@ -3270,57 +3496,61 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>訪問看護</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="D7" s="18" t="n">
-        <v>8.779999999999999</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>26.035</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>109.131</v>
+          <t>訪問入浴介護</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>110.45</v>
+        <v>8.583</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>958.205</v>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
+        <v>0.917</v>
+      </c>
+      <c r="I7" s="12" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="K7" s="12" t="n">
+        <v>17.917</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>訪問リハビリテーション</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="D8" s="18" t="n">
-        <v>11.69</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>13.761</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>53.156</v>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>143.045</v>
-      </c>
-      <c r="H8" s="12" t="n">
-        <v>621.284</v>
-      </c>
+          <t>（2区分）</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="15" t="n">
+        <v>33</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="J8" s="6" t="inlineStr"/>
+      <c r="K8" s="6" t="inlineStr"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
@@ -3330,61 +3560,61 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>通所介護</t>
+          <t>訪問看護</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="n">
-        <v>8.74</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>97.333</v>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>1076</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>39.583</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>64</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0</v>
+        <v>244.5</v>
       </c>
       <c r="H9" s="12" t="n">
-        <v>850.583</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
+        <v>178.917</v>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>110.083</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>197.083</v>
+      </c>
+      <c r="K9" s="12" t="n">
+        <v>241.833</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>通所リハビリテーション</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>83.855</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>189.395</v>
-      </c>
-      <c r="G10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="12" t="n">
-        <v>1350.872</v>
-      </c>
+          <t>（2区分）</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr"/>
+      <c r="C10" s="6" t="inlineStr"/>
+      <c r="D10" s="15" t="n">
+        <v>1076</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>103.583</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr"/>
+      <c r="I10" s="17" t="n">
+        <v>972.417</v>
+      </c>
+      <c r="J10" s="6" t="inlineStr"/>
+      <c r="K10" s="6" t="inlineStr"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
@@ -3394,57 +3624,61 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>短期入所生活介護</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="n">
-        <v>7.89</v>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>11.77</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>25.077</v>
+          <t>訪問リハビリテーション</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>764.667</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>116.333</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>11.223</v>
+        <v>207.917</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>295.245</v>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
+        <v>208.917</v>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>111</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>39.583</v>
+      </c>
+      <c r="K11" s="12" t="n">
+        <v>56.917</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>短期入所療養介護（老健）</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>0.734</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>15.85</v>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>2.568</v>
-      </c>
-      <c r="H12" s="12" t="n">
-        <v>97.31399999999999</v>
-      </c>
+          <t>（2区分）</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr"/>
+      <c r="C12" s="6" t="inlineStr"/>
+      <c r="D12" s="15" t="n">
+        <v>764.667</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>140.333</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="17" t="n">
+        <v>624.333</v>
+      </c>
+      <c r="J12" s="6" t="inlineStr"/>
+      <c r="K12" s="6" t="inlineStr"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
@@ -3454,76 +3688,396 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
+          <t>通所介護</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>850.583</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>417.167</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>164.75</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>107.833</v>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>130.75</v>
+      </c>
+      <c r="K13" s="12" t="n">
+        <v>30.083</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>（2区分）</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="15" t="n">
+        <v>850.583</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="17" t="n">
+        <v>850.583</v>
+      </c>
+      <c r="J14" s="6" t="inlineStr"/>
+      <c r="K14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>通所リハビリテーション</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>1354</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>647.833</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>398.167</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>160.333</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>102.083</v>
+      </c>
+      <c r="K15" s="12" t="n">
+        <v>45.583</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>（2区分）</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr"/>
+      <c r="C16" s="6" t="inlineStr"/>
+      <c r="D16" s="15" t="n">
+        <v>1354</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr"/>
+      <c r="I16" s="17" t="n">
+        <v>1354</v>
+      </c>
+      <c r="J16" s="6" t="inlineStr"/>
+      <c r="K16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>短期入所生活介護</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>306.167</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>2.083</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>76.167</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>112.833</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>57.083</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>34.167</v>
+      </c>
+      <c r="K17" s="12" t="n">
+        <v>14.083</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>（2区分）</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr"/>
+      <c r="C18" s="6" t="inlineStr"/>
+      <c r="D18" s="15" t="n">
+        <v>306.167</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>11.833</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+      <c r="I18" s="17" t="n">
+        <v>294.333</v>
+      </c>
+      <c r="J18" s="6" t="inlineStr"/>
+      <c r="K18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>短期入所療養介護（老健）</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>1.583</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>11.333</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>26.333</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>35.417</v>
+      </c>
+      <c r="K19" s="12" t="n">
+        <v>5.917</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>（2区分）</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="15" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="17" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="J20" s="6" t="inlineStr"/>
+      <c r="K20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
           <t>地域密着型通所介護</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="n">
-        <v>7.89</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>76.167</v>
-      </c>
-      <c r="G13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="12" t="n">
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="n">
         <v>600.667</v>
       </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="E21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>251.333</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>199.417</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>84.417</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>40.917</v>
+      </c>
+      <c r="K21" s="12" t="n">
+        <v>24.583</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>（2区分）</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr"/>
+      <c r="C22" s="6" t="inlineStr"/>
+      <c r="D22" s="15" t="n">
+        <v>600.667</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr"/>
+      <c r="G22" s="6" t="inlineStr"/>
+      <c r="H22" s="6" t="inlineStr"/>
+      <c r="I22" s="17" t="n">
+        <v>600.667</v>
+      </c>
+      <c r="J22" s="6" t="inlineStr"/>
+      <c r="K22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>認知症対応型通所介護</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="12" t="n">
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="n">
         <v>7.917</v>
       </c>
-    </row>
-    <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>注1）★の行の右2列が入力値です。要介護度別の欄がある場合は、03シートの利用者数の構成比で割り振ることになりますが、根拠がないため本表では行っていません。
-注2）要支援の欄が「―」のものは2つに分かれます。①総括表詳細（３）に要支援の行そのものがないもの4件（訪問介護・通所介護・通所リハビリテーション・地域密着型通所介護）。②行はあるが令和7年度の実績値がないもの2件（訪問入浴介護・認知症対応型通所介護）。①の理由は行ごとに異なり（予防給付が総合事業へ移行したもの、予防給付がそもそもないもの、月を単位とする報酬で回数の欄を持たないもの）、当方は総括表の行の有無からしか判別できません。
-注3）年報（様式1の7(17)(19)）のご提供により要介護度別の確定値にできます（確認事項No.134）。</t>
+      <c r="E23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>7.917</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>（2区分）</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr"/>
+      <c r="C24" s="6" t="inlineStr"/>
+      <c r="D24" s="15" t="n">
+        <v>7.917</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr"/>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr"/>
+      <c r="I24" s="17" t="n">
+        <v>7.917</v>
+      </c>
+      <c r="J24" s="6" t="inlineStr"/>
+      <c r="K24" s="6" t="inlineStr"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>注1）★の行（小数）が入力値です。下段の「（2区分）」は、要支援1の位置に要支援計、要介護3の位置に要介護計を置いたものです。
+注2）要支援の欄が0のサービスは、予防給付が総合事業へ移行したもの（訪問介護・通所介護）、予防給付の区分がないもの（地域密着型通所介護・認知症対応型通所介護は要支援の実績が0）、月を単位とする報酬で回（日）数を持たないもの（介護予防通所リハビリテーションは受給者83人／月に対し利用回数が0）です。
+注3）本表は現物給付分です。様式2の審査決定件数（償還払いを含む）とは値が異なります。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A26:K26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3535,7 +4089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3549,21 +4103,21 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>出所の食い違いと本表の限界</t>
+          <t>出所の突合と本表の限界</t>
         </is>
       </c>
     </row>
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>画面の令和7年度の値と総括表の令和7年度の月平均は一致しない。どちらを入力するかで結果が変わるため、食い違いを示す。</t>
+          <t>年報の要介護度別を12で除した月平均が見える化システムの総括表詳細（１）と一致することを確かめ、画面に表示された令和7年度の整数との食い違いを示す。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　施設・居住系　画面の令和7年度と総括表の月平均</t>
+          <t>1　施設・居住系　画面の令和7年度・年報÷12・総括表÷12</t>
         </is>
       </c>
     </row>
@@ -3581,17 +4135,17 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>総括表÷12</t>
+          <t>年報÷12</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>差</t>
+          <t>画面との差</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>総括表÷12との突合</t>
         </is>
       </c>
     </row>
@@ -3605,17 +4159,17 @@
       <c r="C6" s="5" t="n">
         <v>64</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="15" t="n">
         <v>61.5</v>
       </c>
-      <c r="E6" s="19" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>+4.1%</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>2％以上の差</t>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>一致（61.500）</t>
         </is>
       </c>
     </row>
@@ -3629,7 +4183,7 @@
       <c r="C7" s="5" t="n">
         <v>82</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="15" t="n">
         <v>81.583</v>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -3637,7 +4191,11 @@
           <t>+0.5%</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>一致（81.583）</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="6" t="inlineStr"/>
@@ -3649,7 +4207,7 @@
       <c r="C8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -3657,7 +4215,11 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>一致（0.000）</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="6" t="inlineStr"/>
@@ -3669,7 +4231,7 @@
       <c r="C9" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="15" t="n">
         <v>59.25</v>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -3677,7 +4239,11 @@
           <t>+1.3%</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>一致（59.250）</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="6" t="inlineStr"/>
@@ -3689,7 +4255,7 @@
       <c r="C10" s="5" t="n">
         <v>140</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="15" t="n">
         <v>138.25</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -3697,7 +4263,11 @@
           <t>+1.3%</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>一致（138.250）</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="6" t="inlineStr"/>
@@ -3709,17 +4279,17 @@
       <c r="C11" s="5" t="n">
         <v>130</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="15" t="n">
         <v>134.083</v>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>-3.0%</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>2％以上の差</t>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>一致（134.083）</t>
         </is>
       </c>
     </row>
@@ -3733,26 +4303,26 @@
       <c r="C12" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="15" t="n">
         <v>5.5</v>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>+9.1%</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>2％以上の差</t>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>一致（5.500）</t>
         </is>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>注1）2％以上の差があるのは3件（特定施設入居者生活介護・介護老人保健施設・介護医療院）です。
-注2）総括表詳細（１）の利用者数に総括表詳細（４）の1人1月あたり給付費を乗じると総括表詳細（５）の給付費になり、その合計は年報の給付費と円単位で一致します（令和7年度 2,915,307,125円）。総括表は年報に紐づく系列です。
-注3）画面の令和7年度がどの系列によるものかは、当方は確かめられていません。年報のご提供により確かめられます。</t>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>注1）画面の整数と2％以上の差があるのは3件（特定施設入居者生活介護・介護老人保健施設・介護医療院）です。
+注2）年報の要介護度別を12で除した月平均は総括表詳細（１）の令和7年度と一致します。総括表詳細（１）の利用者数に総括表詳細（４）の1人1月あたり給付費を乗じると総括表詳細（５）の給付費になり、その合計は年報の給付費と円単位で一致します（令和7年度 2,915,307,125円）。年報・総括表・給付費が一つの系列でつながっています。
+注3）画面に表示された令和7年度の整数はこの系列と食い違います。当方は画面の値がどのように作られているかを確かめられていません（確認事項No.136）。本表は年報の値を用いています。</t>
         </is>
       </c>
     </row>
@@ -3789,17 +4359,17 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>要介護度別の内訳が推定値である</t>
+          <t>画面の令和7年度との食い違いを説明できない</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>②③の要介護度別は按分による。サービス計は確定値である</t>
+          <t>特定施設入居者生活介護で＋4.1％、介護老人保健施設で▲3.0％、介護医療院で＋9.1％の差がある。年報の側は要介護度別の和・総括表・給付費の三つで内的整合が取れている</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>年報（様式1の6・様式1の7・様式2）の要介護度別のご提供</t>
+          <t>見える化システム側の作り方のご確認（確認事項No.136）</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr"/>
@@ -3811,17 +4381,17 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>①の性別・年齢階級別の内訳がない</t>
+          <t>令和8年度が実際に減っているかを分けられない</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>画面が性別・年齢階級別の入力を求める場合は用意できない</t>
+          <t>介護老人保健施設は令和7年度から令和8年度へ14.6％減っている。季節の効き（施設は冬季が2.80％高い）では説明できない。実際の減少であれば令和7年度を置くと過大になる</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>年報（様式1の5）のご提供</t>
+          <t>休止床・改修・職員の状況のご確認（確認事項No.133）</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr"/>
@@ -3833,17 +4403,17 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>④を要介護度別に分けられない</t>
+          <t>入力欄が小数を受け付けるかが分からない</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>総括表詳細（３）は要支援・要介護の2区分である</t>
+          <t>整数に丸めると定期巡回・随時対応型訪問介護看護（月0.583人）と認知症対応型通所介護（月1.000人）が0又は1に落ちる</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>年報（様式1の7(17)(19)）のご提供</t>
+          <t>画面でのご確認（確認事項No.135）</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr"/>
@@ -3855,17 +4425,17 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度との食い違いを説明できない</t>
+          <t>令和8年度の月報との接続を検算していない</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>特定施設入居者生活介護で＋4.1％、介護老人保健施設で▲3.0％の差がある</t>
+          <t>令和8年度の実績見込み値を置き換えるのであって、令和8年4月から7月までの月報そのものは変えない。画面が月報から再計算する作りであれば入力値が戻る可能性がある</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>年報との突合</t>
+          <t>入力後の画面の表示のご確認</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr"/>
@@ -3877,24 +4447,468 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>令和8年度が実際に減っているかを分けられない</t>
+          <t>第2号被保険者の扱いを画面側で確かめていない</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設は令和7年度から令和8年度へ14.6％減っている。季節の効き（施設は冬季が2.80％高い）では説明できない。実際の減少であれば令和7年度を置くと過大になる</t>
+          <t>②③④は第1号・第2号の総数である（第2号は介護老人保健施設に年間の延べ15人など）。画面が第1号のみを求める場合は値が異なる</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>休止床・改修・職員の状況のご確認（確認事項No.133）</t>
+          <t>画面の表示のご確認。年報から第1号のみの値も出せる</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr"/>
       <c r="F22" s="6" t="inlineStr"/>
     </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>3　在宅サービス　年報÷12と総括表÷12の突合</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="4" t="inlineStr"/>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>サービス</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>年報÷12</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>総括表÷12</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>差</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>出所</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="6" t="inlineStr"/>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>270.083</v>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>270.083</v>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>様式1の7</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="6" t="inlineStr"/>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>訪問入浴介護</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D27" s="15" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>様式1の7</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="6" t="inlineStr"/>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>訪問看護</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="n">
+        <v>135.167</v>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>135.167</v>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>様式1の7</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="6" t="inlineStr"/>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>訪問リハビリテーション</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="n">
+        <v>66.917</v>
+      </c>
+      <c r="D29" s="15" t="n">
+        <v>66.917</v>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>様式1の7</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="6" t="inlineStr"/>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>居宅療養管理指導</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="n">
+        <v>193.25</v>
+      </c>
+      <c r="D30" s="15" t="n">
+        <v>193.25</v>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>様式1の7</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="6" t="inlineStr"/>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>通所介護</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="n">
+        <v>97.333</v>
+      </c>
+      <c r="D31" s="15" t="n">
+        <v>97.333</v>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>様式1の7</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="6" t="inlineStr"/>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>通所リハビリテーション</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="n">
+        <v>273.25</v>
+      </c>
+      <c r="D32" s="15" t="n">
+        <v>273.25</v>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>様式1の7</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="6" t="inlineStr"/>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>短期入所生活介護</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D33" s="15" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>様式1の7</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="6" t="inlineStr"/>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>短期入所療養介護（老健）</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="n">
+        <v>16.583</v>
+      </c>
+      <c r="D34" s="15" t="n">
+        <v>16.583</v>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>様式1の7</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="6" t="inlineStr"/>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>福祉用具貸与</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="n">
+        <v>642.083</v>
+      </c>
+      <c r="D35" s="15" t="n">
+        <v>642.083</v>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>様式1の7</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="6" t="inlineStr"/>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>特定福祉用具購入費</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="D36" s="15" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>様式2（件数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="6" t="inlineStr"/>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>住宅改修費</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="n">
+        <v>8.417</v>
+      </c>
+      <c r="D37" s="15" t="n">
+        <v>8.417</v>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>様式2（件数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="6" t="inlineStr"/>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>介護予防支援・居宅介護支援</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="n">
+        <v>913.333</v>
+      </c>
+      <c r="D38" s="15" t="n">
+        <v>913.333</v>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>様式1の7</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="6" t="inlineStr"/>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>定期巡回・随時対応型訪問介護看護</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="D39" s="15" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>様式1の7</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="6" t="inlineStr"/>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型通所介護</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="n">
+        <v>76.167</v>
+      </c>
+      <c r="D40" s="15" t="n">
+        <v>76.167</v>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>様式1の7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="6" t="inlineStr"/>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型通所介護</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>様式1の7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="6" t="inlineStr"/>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>小規模多機能型居宅介護</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="n">
+        <v>99.917</v>
+      </c>
+      <c r="D42" s="15" t="n">
+        <v>99.917</v>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>様式1の7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A14:F14"/>
@@ -3911,7 +4925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3996,7 +5010,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の要介護度別の和がサービス計と一致すること</t>
+          <t>施設・居住系　年報の要介護度別の和÷12が総括表詳細（１）と一致すること</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -4006,7 +5020,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>全件一致</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -4022,7 +5036,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>在宅の要介護度別の和がサービス計と一致すること</t>
+          <t>在宅　年報の要介護度別の和÷12が総括表詳細（１）と一致すること</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -4032,7 +5046,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>全件一致</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -4100,17 +5114,17 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>利用率×在宅認定者数が総括表の月平均に近いこと（訪問介護で確かめる）</t>
+          <t>画面の利用率×在宅認定者数が年報の月平均に近いこと（訪問介護で確かめる。分母の見立てが正しいかの点検）</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>利用率×認定者数 268.4人</t>
+          <t>利用率×認定者数 267.3人</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>総括表÷12 270.08人（差-0.6%）</t>
+          <t>年報÷12 270.08人（差-1.0%）</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -4178,7 +5192,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度と総括表の月平均に2％以上の差があるものを示していること</t>
+          <t>画面の令和7年度と年報の月平均に2％以上の差があるものを示していること</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -4204,17 +5218,17 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>④の利用回（日）数が要支援・要介護の2区分にとどまること</t>
+          <t>④の利用回（日）数を要介護度別に出していること</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>総括表詳細（３）の区分</t>
+          <t>様式1の7(17)(19)</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>10サービス。要介護度別には分けていない</t>
+          <t>10サービス。要支援・要介護の2区分の計も併記</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -4230,17 +5244,17 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>利用率が全欄0.0％のサービスを認定者数で按分し、そのことを注記していること</t>
+          <t>④を利用者数で除した1人1月あたり利用回（日）数が総括表詳細（３）と3％以内で一致すること</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>在宅17サービス</t>
+          <t>10サービス×要支援・要介護</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>1件：定期巡回・随時対応型訪問介護看護（月平均0.583人。利用率の刻み0.1％＝約1.5人に満たない）</t>
+          <t>全件一致</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -4250,43 +5264,97 @@
       </c>
       <c r="F15" s="6" t="inlineStr"/>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="11" t="inlineStr"/>
-      <c r="B16" s="11" t="inlineStr">
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>画面が「―」を表示している要介護度に年報の実績がないこと</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>施設・居住系7サービス×7区分</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>実績のある欄はない</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>第2号被保険者を含む値であることを明示していること</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>様式1の6(15)の第2号</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>介護老人保健施設に年間の延べ15人（第1号1,594＋第2号15＝1,609）。02シート注4に記載</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="10" t="inlineStr"/>
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>11件</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>適合11件・不適合0件</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>13件</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>適合13件・不適合0件</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr"/>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>注1）点検6は、在宅の要介護度別の按分の方法が成り立つかを確かめるものです。利用率に在宅の認定者数を乗じた値が総括表の月平均とほぼ一致すれば、同じ重みで按分してよいことになります。
-注2）1件でも不適合があると、本表を作るスクリプトは終了コード1で終わります。</t>
+      <c r="F18" s="10" t="inlineStr"/>
+    </row>
+    <row r="20" ht="56" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>注1）点検2・3が本表の要です。年報の要介護度別を12で除して足した値が、見える化システムの総括表詳細（１）の令和7年度と施設・居住系7サービス・在宅17サービスのすべてで一致します（許容0.0005人）。年報と総括表が同じ系列であることが確かめられ、要介護度別の内訳を確定値として扱えます。
+注2）点検11は、④を③で除して1人1月あたりに戻したとき総括表詳細（３）と一致するかの点検です。④と③が同じ集計から出ていることを確かめています。
+注3）点検6は、画面に表示される在宅サービス利用率の分母が在宅の認定者数であるという見立てを確かめるものです。本表の入力値はこの按分によるものではありません。
+注4）1件でも不適合があると、本表を作るスクリプトは終了コード1で終わります。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A20:F20"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4363,28 +5431,27 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>年報（令和7年度）の様式別データのご提供</t>
+          <t>年報（令和7年度）の様式別データのご提供　→　取下げ</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の実績見込み値を令和7年度に差し替えるに当たり、要介護度別の確定値を作るには年報（令和7年度）の次の様式が必要である。①様式1の5（要介護（要支援）認定者数。性別・年齢階級別）、②様式1の6（15）及び様式1の7（16）（18）（サービス別・要介護度別の受給者数）、③様式1の7（17）（19）（同 利用回（日）数）、④様式2（件数）。現在、当方はサービス計（総括表詳細（１）÷12）までは確定値で出せるが、要介護度別の内訳は按分による推定値である。Excelの形でご提供いただければ、要介護度別に合計すると総括表の令和7年度と一致することを検算したうえで確定値をお渡しできる。</t>
+          <t>令和8年9月11日、年報（令和7年度）の全様式を電子データで確認した。本確認事項で求めていた様式1の5・様式1の6(15)・様式1の7(16)〜(19)・様式2はいずれも同データに収められており、②③④の要介護度別を確定値にできた。当該データは令和8年8月28日に受領済みの資料No.22と同一のものであり、当方が主要値のみを取り込み、サービス種別×要介護度の明細を取り込んでいなかったことによる。本確認事項は当方の取込漏れによるものであるため取り下げる。明細は `data_nenpo_meisai.py` に収め、12で除した値が総括表詳細（１）と全24サービスで一致することを検算した。</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階
-サービス見込量 第1次概算</t>
+          <t>（解消済み）</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>―</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -4428,12 +5495,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度と総括表の月平均の食い違い</t>
+          <t>画面の令和7年度と年報の月平均の食い違い</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の令和7年度について、画面に表示された値と総括表詳細（１）の年間の延べ人月を12で除した値が一致しない。特定施設入居者生活介護は画面64人・総括表61.50人（＋4.1％）、介護老人保健施設は画面130人・総括表134.08人（▲3.0％）である。総括表は利用者数×1人あたり給付費＝給付費が全行で成立し、その合計が年報の給付費と円単位で一致する系列である。当方は総括表を用いる整理としたが、画面の値がどの系列によるものかを確かめられていない。年報のご提供（確認事項No.134）により確かめる。</t>
+          <t>施設・居住系の令和7年度について、画面に表示された値と年報の要介護度別を12で除した値が一致しない。特定施設入居者生活介護は画面64人・年報61.50人（＋4.1％）、介護老人保健施設は画面130人・年報134.08人（▲3.0％）、介護医療院は画面6人・年報5.50人（＋9.1％）である。年報の側は、要介護度別の和÷12が総括表詳細（１）と全24サービスで一致し、総括表の給付費の合計が年報の給付費と円単位で一致する（令和7年度 2,915,307,125円）。画面の整数がどのように作られているかを当方は確かめられていない。①画面の値の作り方をご確認いただきたい（保険者単位と3町合計の違い、時点の違い、現物給付分と償還払いを含む件数の違いのいずれか）。②本表は年報の値を用いる整理としてよいかご判断いただきたい。③画面の令和7年度は要介護度別の和と合計欄が1人ずれる行があり（特定施設63対64、介護老人福祉施設141対140）、画面の値をそのまま貼ると誤差が入る。</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -4453,11 +5520,12 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>注1）本表により新たに起票した確認事項は3件（No.134〜No.136）です。既に起票済みのNo.128（実績見込み値を編集するか）・No.132（在宅の編集画面の現在値）・No.133（介護老人保健施設の減少）とも関わります。
-注2）確認事項は業務工程管理表 03_確認事項一覧で一元管理します。</t>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>注1）本表に係る確認事項は3件（No.134〜No.136）で、うちNo.134は解消により取り下げます。ご確認をお願いするのはNo.135・No.136の2件です。
+注2）既に起票済みのNo.128（実績見込み値を編集するか）・No.132（在宅の編集画面の現在値）・No.133（介護老人保健施設の減少）とも関わります。No.132（在宅の編集画面の現在値のご提供）は、年報により入力値が確定したため、画面の並びに合わせるための参考にとどまります。
+注3）確認事項は業務工程管理表 03_確認事項一覧で一元管理します。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx
+++ b/output/第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx
@@ -23,8 +23,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -66,7 +67,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -91,6 +92,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -130,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -152,6 +158,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -164,7 +173,7 @@
     <xf numFmtId="164" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -176,10 +185,19 @@
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -550,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -758,12 +776,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>整数に丸めると小口のサービスが0に落ちる</t>
+          <t>人数の欄は整数で扱われるため丸め方で小口が消える</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護は月平均0.583人、認知症対応型通所介護は月平均1.000人である。0を入れると令和9年度から令和11年度も0のまま残る。本表は小数版と整数版の両方を用意している</t>
+          <t>定期巡回・随時対応型訪問介護看護は月平均0.583人、認知症対応型通所介護は月平均1.000人である。各欄を単純に四捨五入すると全欄が0になり、令和9年度から令和11年度も0のまま残る。本表の整数版は群（要支援・要介護）ごとに合計を保つため0にはならない（05シート1）</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr"/>
@@ -803,11 +821,151 @@
       <c r="D18" s="6" t="inlineStr"/>
       <c r="E18" s="6" t="inlineStr"/>
     </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>3　入力に併せて設定する項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="4" t="inlineStr"/>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>設定項目</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>当方の案</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22" ht="62" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>利用者数（人数）の欄</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>整数版（02・03シートの下段）を入力する</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>人数の欄は整数で扱われる。小数を入れても令和9年度から令和11年度の推計値は整数で出る。整数版は最大剰余法により要支援・要介護の群ごとの合計を保つため、定期巡回・随時対応型訪問介護看護（月0.583人）は要介護5に1人が立ち、0にはならない</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23" ht="62" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>利用回（日）数の欄</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>小数第1位版（04シートの★の行）を入力する</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>利用回（日）数の欄は小数第1位まで受け付ける</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24" ht="62" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>実績見込み値を編集した理由の記入欄</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>「令和8年度の実績が4か月分であるため」</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>設定内容を記入する欄が画面にある。記入した内容は推計結果の出力に「施策反映の内容」として載る。後日の説明のために記入しておく</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="62" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>認定率の伸び・利用率の伸びの選択</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>「当該市町村における令和6年度→令和7年度の伸び」を選ぶ</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度を含まない唯一の選択肢である。令和8年度は4か月であり、在宅は夏季に偏る（当方の検証では在宅は冬季が夏季より2.48％低い）</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26" ht="62" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり給付費の実績値の年度</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>［要協議］令和7年度を選ぶ案</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>令和7年度か令和8年度かを選ぶ項目がある。当方の検証では単価は改定の有無に関係なく年率1.75％で伸びており、令和7年度で固定することは月額で＋185〜＋374円に当たる。施設・居住系と在宅で別に選べるため、そろえるかどうかを含めご判断いただきたい（確認事項No.137）</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr"/>
+    </row>
+    <row r="28" ht="14" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>注）本節の①から⑤までは、弊社の別案件において実際に小数を入力して出力された推計結果により確かめたものです。その保険者の数値は用いていません。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A28:E28"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A13:E13"/>
   </mergeCells>
@@ -908,42 +1066,42 @@
           <t>認定者数（人）</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="10" t="n">
         <v>298</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="10" t="n">
         <v>292</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="10" t="n">
         <v>515</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="10" t="n">
         <v>299</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="10" t="n">
         <v>212</v>
       </c>
-      <c r="H5" s="9" t="n">
+      <c r="H5" s="10" t="n">
         <v>213</v>
       </c>
-      <c r="I5" s="9" t="n">
+      <c r="I5" s="10" t="n">
         <v>155</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="10" t="inlineStr"/>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr"/>
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr"/>
-      <c r="D6" s="10" t="inlineStr"/>
-      <c r="E6" s="10" t="inlineStr"/>
-      <c r="F6" s="10" t="inlineStr"/>
-      <c r="G6" s="10" t="inlineStr"/>
-      <c r="H6" s="10" t="inlineStr"/>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr"/>
+      <c r="D6" s="11" t="inlineStr"/>
+      <c r="E6" s="11" t="inlineStr"/>
+      <c r="F6" s="11" t="inlineStr"/>
+      <c r="G6" s="11" t="inlineStr"/>
+      <c r="H6" s="11" t="inlineStr"/>
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>第1号被保険者 1,984人（要支援 590人・要介護 1,394人）。第2号被保険者 36人</t>
         </is>
@@ -1197,34 +1355,34 @@
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="10" t="inlineStr"/>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr"/>
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="C16" s="12" t="n">
         <v>298</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="12" t="n">
         <v>292</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E16" s="12" t="n">
         <v>515</v>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="F16" s="12" t="n">
         <v>299</v>
       </c>
-      <c r="G16" s="11" t="n">
+      <c r="G16" s="12" t="n">
         <v>212</v>
       </c>
-      <c r="H16" s="11" t="n">
+      <c r="H16" s="12" t="n">
         <v>213</v>
       </c>
-      <c r="I16" s="11" t="n">
+      <c r="I16" s="12" t="n">
         <v>155</v>
       </c>
-      <c r="J16" s="11" t="n">
+      <c r="J16" s="12" t="n">
         <v>1984</v>
       </c>
     </row>
@@ -1353,28 +1511,28 @@
           <t>特定施設入居者生活介護</t>
         </is>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="13" t="n">
         <v>61.5</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="F5" s="12" t="n">
+      <c r="F5" s="13" t="n">
         <v>5.333</v>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="13" t="n">
         <v>14.917</v>
       </c>
-      <c r="H5" s="12" t="n">
+      <c r="H5" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="I5" s="12" t="n">
+      <c r="I5" s="13" t="n">
         <v>8.167</v>
       </c>
-      <c r="J5" s="12" t="n">
+      <c r="J5" s="13" t="n">
         <v>10.75</v>
       </c>
-      <c r="K5" s="12" t="n">
+      <c r="K5" s="13" t="n">
         <v>6.333</v>
       </c>
     </row>
@@ -1386,28 +1544,28 @@
       </c>
       <c r="B6" s="6" t="inlineStr"/>
       <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="14" t="n">
         <v>62</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="G6" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="H6" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="I6" s="13" t="n">
+      <c r="I6" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="J6" s="13" t="n">
+      <c r="J6" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="K6" s="13" t="n">
+      <c r="K6" s="14" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1427,28 +1585,28 @@
           <t>認知症対応型共同生活介護</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="13" t="n">
         <v>81.583</v>
       </c>
-      <c r="E7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="12" t="n">
+      <c r="E7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="13" t="n">
         <v>0.417</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="H7" s="12" t="n">
+      <c r="H7" s="13" t="n">
         <v>18.667</v>
       </c>
-      <c r="I7" s="12" t="n">
+      <c r="I7" s="13" t="n">
         <v>21.75</v>
       </c>
-      <c r="J7" s="12" t="n">
+      <c r="J7" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="K7" s="12" t="n">
+      <c r="K7" s="13" t="n">
         <v>13.75</v>
       </c>
     </row>
@@ -1460,28 +1618,28 @@
       </c>
       <c r="B8" s="6" t="inlineStr"/>
       <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="14" t="n">
         <v>82</v>
       </c>
-      <c r="E8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="13" t="n">
+      <c r="E8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="H8" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="I8" s="13" t="n">
+      <c r="I8" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="J8" s="13" t="n">
+      <c r="J8" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="K8" s="13" t="n">
+      <c r="K8" s="14" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1501,28 +1659,28 @@
           <t>地域密着型特定施設入居者生活介護</t>
         </is>
       </c>
-      <c r="D9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="12" t="n">
+      <c r="D9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1534,28 +1692,28 @@
       </c>
       <c r="B10" s="6" t="inlineStr"/>
       <c r="C10" s="6" t="inlineStr"/>
-      <c r="D10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="13" t="n">
+      <c r="D10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1575,28 +1733,28 @@
           <t>地域密着型介護老人福祉施設入所者生活介護</t>
         </is>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="13" t="n">
         <v>59.25</v>
       </c>
-      <c r="E11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="12" t="n">
+      <c r="E11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="13" t="n">
         <v>2.167</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="H11" s="13" t="n">
         <v>10.667</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="I11" s="13" t="n">
         <v>10.167</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="J11" s="13" t="n">
         <v>21.417</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="K11" s="13" t="n">
         <v>14.833</v>
       </c>
     </row>
@@ -1608,28 +1766,28 @@
       </c>
       <c r="B12" s="6" t="inlineStr"/>
       <c r="C12" s="6" t="inlineStr"/>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="14" t="n">
         <v>59</v>
       </c>
-      <c r="E12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="13" t="n">
+      <c r="E12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="H12" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="I12" s="13" t="n">
+      <c r="I12" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="J12" s="13" t="n">
+      <c r="J12" s="14" t="n">
         <v>21</v>
       </c>
-      <c r="K12" s="13" t="n">
+      <c r="K12" s="14" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1649,28 +1807,28 @@
           <t>介護老人福祉施設</t>
         </is>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="13" t="n">
         <v>138.25</v>
       </c>
-      <c r="E13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="12" t="n">
+      <c r="E13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="13" t="n">
         <v>5.75</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="H13" s="13" t="n">
         <v>18.333</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="I13" s="13" t="n">
         <v>43</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="J13" s="13" t="n">
         <v>46.333</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="K13" s="13" t="n">
         <v>24.833</v>
       </c>
     </row>
@@ -1682,28 +1840,28 @@
       </c>
       <c r="B14" s="6" t="inlineStr"/>
       <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="14" t="n">
         <v>138</v>
       </c>
-      <c r="E14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="13" t="n">
+      <c r="E14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="H14" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="I14" s="13" t="n">
+      <c r="I14" s="14" t="n">
         <v>43</v>
       </c>
-      <c r="J14" s="13" t="n">
+      <c r="J14" s="14" t="n">
         <v>46</v>
       </c>
-      <c r="K14" s="13" t="n">
+      <c r="K14" s="14" t="n">
         <v>25</v>
       </c>
     </row>
@@ -1723,28 +1881,28 @@
           <t>介護老人保健施設</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="13" t="n">
         <v>134.083</v>
       </c>
-      <c r="E15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="12" t="n">
+      <c r="E15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="13" t="n">
         <v>30.5</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="H15" s="13" t="n">
         <v>30.917</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="I15" s="13" t="n">
         <v>25.5</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="J15" s="13" t="n">
         <v>33.167</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="K15" s="13" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1756,28 +1914,28 @@
       </c>
       <c r="B16" s="6" t="inlineStr"/>
       <c r="C16" s="6" t="inlineStr"/>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="14" t="n">
         <v>134</v>
       </c>
-      <c r="E16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="13" t="n">
+      <c r="E16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14" t="n">
         <v>31</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="H16" s="14" t="n">
         <v>31</v>
       </c>
-      <c r="I16" s="13" t="n">
+      <c r="I16" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="J16" s="13" t="n">
+      <c r="J16" s="14" t="n">
         <v>33</v>
       </c>
-      <c r="K16" s="13" t="n">
+      <c r="K16" s="14" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1797,28 +1955,28 @@
           <t>介護医療院</t>
         </is>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="13" t="n">
         <v>5.5</v>
       </c>
-      <c r="E17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="12" t="n">
+      <c r="E17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="13" t="n">
         <v>0.083</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="K17" s="13" t="n">
         <v>5.417</v>
       </c>
     </row>
@@ -1830,68 +1988,68 @@
       </c>
       <c r="B18" s="6" t="inlineStr"/>
       <c r="C18" s="6" t="inlineStr"/>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="E18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="13" t="n">
+      <c r="E18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="14" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="10" t="inlineStr"/>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr"/>
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr"/>
-      <c r="D19" s="14" t="n">
+      <c r="C19" s="11" t="inlineStr"/>
+      <c r="D19" s="15" t="n">
         <v>480.167</v>
       </c>
-      <c r="E19" s="14" t="n">
+      <c r="E19" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="F19" s="14" t="n">
+      <c r="F19" s="15" t="n">
         <v>5.75</v>
       </c>
-      <c r="G19" s="14" t="n">
+      <c r="G19" s="15" t="n">
         <v>65.333</v>
       </c>
-      <c r="H19" s="14" t="n">
+      <c r="H19" s="15" t="n">
         <v>86.583</v>
       </c>
-      <c r="I19" s="14" t="n">
+      <c r="I19" s="15" t="n">
         <v>108.583</v>
       </c>
-      <c r="J19" s="14" t="n">
+      <c r="J19" s="15" t="n">
         <v>126.75</v>
       </c>
-      <c r="K19" s="14" t="n">
+      <c r="K19" s="15" t="n">
         <v>79.167</v>
       </c>
     </row>
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>注1）★の行（小数）が入力値です。入力欄が整数しか受け付けない場合は下段の整数を用います。
+          <t>注1）人数の欄は整数で扱われるため、下段の「（整数）」が入力値です（00シート3参照）。上段の★の行は年報の値を12で除したそのままの値で、整数版はこれを群（要支援・要介護）ごとに合計を保って丸めたものです。
 注2）施設・居住系の計は480.167人です。画面の令和8年度（4か月）は474人、画面の令和7年度は482人です。
 注3）地域密着型特定施設入居者生活介護は区域内に事業所がなく0です。認知症対応型共同生活介護と特定施設入居者生活介護は短期利用の欄が年報にありますが、いずれも実績は0です。
 注4）施設サービス（特養・老健・介護医療院）は第2号被保険者を含みます。第2号は介護老人保健施設に15人（年間の延べ人数）のみです。</t>
@@ -2037,28 +2195,28 @@
           <t>施設・居住系の利用者数</t>
         </is>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="16" t="n">
         <v>480.167</v>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="16" t="n">
         <v>5.75</v>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="F7" s="16" t="n">
         <v>65.333</v>
       </c>
-      <c r="G7" s="15" t="n">
+      <c r="G7" s="16" t="n">
         <v>86.583</v>
       </c>
-      <c r="H7" s="15" t="n">
+      <c r="H7" s="16" t="n">
         <v>108.583</v>
       </c>
-      <c r="I7" s="15" t="n">
+      <c r="I7" s="16" t="n">
         <v>126.75</v>
       </c>
-      <c r="J7" s="15" t="n">
+      <c r="J7" s="16" t="n">
         <v>79.167</v>
       </c>
     </row>
@@ -2069,28 +2227,28 @@
           <t>在宅の認定者数（差引き）</t>
         </is>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>1503.833</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>290</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>286.25</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="17" t="n">
         <v>449.667</v>
       </c>
-      <c r="G8" s="16" t="n">
+      <c r="G8" s="17" t="n">
         <v>212.417</v>
       </c>
-      <c r="H8" s="16" t="n">
+      <c r="H8" s="17" t="n">
         <v>103.417</v>
       </c>
-      <c r="I8" s="16" t="n">
+      <c r="I8" s="17" t="n">
         <v>86.25</v>
       </c>
-      <c r="J8" s="16" t="n">
+      <c r="J8" s="17" t="n">
         <v>75.833</v>
       </c>
     </row>
@@ -2104,7 +2262,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2　入力値（上段が小数、下段が整数）</t>
+          <t>2　入力値（上段が実数、下段の整数が入力値）</t>
         </is>
       </c>
     </row>
@@ -2167,28 +2325,28 @@
           <t>訪問介護</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C14" s="13" t="n">
         <v>270.083</v>
       </c>
-      <c r="D14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="12" t="n">
+      <c r="D14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="13" t="n">
         <v>99.917</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="G14" s="13" t="n">
         <v>49.667</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="H14" s="13" t="n">
         <v>42.583</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="I14" s="13" t="n">
         <v>44.417</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="J14" s="13" t="n">
         <v>33.5</v>
       </c>
     </row>
@@ -2199,28 +2357,28 @@
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr"/>
-      <c r="C15" s="13" t="n">
+      <c r="C15" s="14" t="n">
         <v>270</v>
       </c>
-      <c r="D15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="13" t="n">
+      <c r="D15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="G15" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="H15" s="14" t="n">
         <v>43</v>
       </c>
-      <c r="I15" s="13" t="n">
+      <c r="I15" s="14" t="n">
         <v>44</v>
       </c>
-      <c r="J15" s="13" t="n">
+      <c r="J15" s="14" t="n">
         <v>33</v>
       </c>
     </row>
@@ -2235,28 +2393,28 @@
           <t>訪問入浴介護</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C16" s="13" t="n">
         <v>5.25</v>
       </c>
-      <c r="D16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="12" t="n">
+      <c r="D16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="13" t="n">
         <v>1.167</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="G16" s="13" t="n">
         <v>0.25</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="H16" s="13" t="n">
         <v>0.25</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="I16" s="13" t="n">
         <v>1.167</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="J16" s="13" t="n">
         <v>2.417</v>
       </c>
     </row>
@@ -2267,28 +2425,28 @@
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr"/>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="D17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="13" t="n">
+      <c r="D17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="13" t="n">
+      <c r="G17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="J17" s="13" t="n">
+      <c r="J17" s="14" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2303,28 +2461,28 @@
           <t>訪問看護</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="C18" s="13" t="n">
         <v>135.167</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="13" t="n">
         <v>10.25</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="13" t="n">
         <v>14.167</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="F18" s="13" t="n">
         <v>41.083</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="G18" s="13" t="n">
         <v>25.417</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="H18" s="13" t="n">
         <v>13.833</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="I18" s="13" t="n">
         <v>15.167</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="J18" s="13" t="n">
         <v>15.25</v>
       </c>
     </row>
@@ -2335,28 +2493,28 @@
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr"/>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="14" t="n">
         <v>135</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="E19" s="13" t="n">
+      <c r="E19" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="F19" s="14" t="n">
         <v>41</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="G19" s="14" t="n">
         <v>26</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="H19" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="I19" s="13" t="n">
+      <c r="I19" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="J19" s="13" t="n">
+      <c r="J19" s="14" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2371,28 +2529,28 @@
           <t>訪問リハビリテーション</t>
         </is>
       </c>
-      <c r="C20" s="12" t="n">
+      <c r="C20" s="13" t="n">
         <v>66.917</v>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="D20" s="13" t="n">
         <v>3.167</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="13" t="n">
         <v>10.333</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="F20" s="13" t="n">
         <v>20.25</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="G20" s="13" t="n">
         <v>16.833</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="H20" s="13" t="n">
         <v>7.833</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="I20" s="13" t="n">
         <v>3.833</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="J20" s="13" t="n">
         <v>4.667</v>
       </c>
     </row>
@@ -2403,28 +2561,28 @@
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr"/>
-      <c r="C21" s="13" t="n">
+      <c r="C21" s="14" t="n">
         <v>67</v>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="E21" s="13" t="n">
+      <c r="E21" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="F21" s="13" t="n">
+      <c r="F21" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="G21" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="H21" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="I21" s="13" t="n">
+      <c r="I21" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="J21" s="13" t="n">
+      <c r="J21" s="14" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2439,28 +2597,28 @@
           <t>居宅療養管理指導</t>
         </is>
       </c>
-      <c r="C22" s="12" t="n">
+      <c r="C22" s="13" t="n">
         <v>193.25</v>
       </c>
-      <c r="D22" s="12" t="n">
+      <c r="D22" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="F22" s="13" t="n">
         <v>37.5</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="G22" s="13" t="n">
         <v>31.083</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="H22" s="13" t="n">
         <v>37.5</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="I22" s="13" t="n">
         <v>39.833</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="J22" s="13" t="n">
         <v>33.333</v>
       </c>
     </row>
@@ -2471,28 +2629,28 @@
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr"/>
-      <c r="C23" s="13" t="n">
+      <c r="C23" s="14" t="n">
         <v>193</v>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="E23" s="13" t="n">
+      <c r="E23" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="F23" s="13" t="n">
+      <c r="F23" s="14" t="n">
         <v>38</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="G23" s="14" t="n">
         <v>31</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="H23" s="14" t="n">
         <v>37</v>
       </c>
-      <c r="I23" s="13" t="n">
+      <c r="I23" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="J23" s="13" t="n">
+      <c r="J23" s="14" t="n">
         <v>33</v>
       </c>
     </row>
@@ -2507,28 +2665,28 @@
           <t>通所介護</t>
         </is>
       </c>
-      <c r="C24" s="12" t="n">
+      <c r="C24" s="13" t="n">
         <v>97.333</v>
       </c>
-      <c r="D24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="12" t="n">
+      <c r="D24" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="13" t="n">
         <v>49.667</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="G24" s="13" t="n">
         <v>22.083</v>
       </c>
-      <c r="H24" s="12" t="n">
+      <c r="H24" s="13" t="n">
         <v>10.75</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="I24" s="13" t="n">
         <v>11.667</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="J24" s="13" t="n">
         <v>3.167</v>
       </c>
     </row>
@@ -2539,28 +2697,28 @@
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr"/>
-      <c r="C25" s="13" t="n">
+      <c r="C25" s="14" t="n">
         <v>97</v>
       </c>
-      <c r="D25" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="13" t="n">
+      <c r="D25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="14" t="n">
         <v>49</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="G25" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="H25" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="I25" s="13" t="n">
+      <c r="I25" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="J25" s="13" t="n">
+      <c r="J25" s="14" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2575,28 +2733,28 @@
           <t>通所リハビリテーション</t>
         </is>
       </c>
-      <c r="C26" s="12" t="n">
+      <c r="C26" s="13" t="n">
         <v>273.25</v>
       </c>
-      <c r="D26" s="12" t="n">
+      <c r="D26" s="13" t="n">
         <v>31.167</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="13" t="n">
         <v>52.25</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="F26" s="13" t="n">
         <v>97.75</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="G26" s="13" t="n">
         <v>51.917</v>
       </c>
-      <c r="H26" s="12" t="n">
+      <c r="H26" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="I26" s="12" t="n">
+      <c r="I26" s="13" t="n">
         <v>13.5</v>
       </c>
-      <c r="J26" s="12" t="n">
+      <c r="J26" s="13" t="n">
         <v>6.667</v>
       </c>
     </row>
@@ -2607,28 +2765,28 @@
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr"/>
-      <c r="C27" s="13" t="n">
+      <c r="C27" s="14" t="n">
         <v>273</v>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D27" s="14" t="n">
         <v>31</v>
       </c>
-      <c r="E27" s="13" t="n">
+      <c r="E27" s="14" t="n">
         <v>52</v>
       </c>
-      <c r="F27" s="13" t="n">
+      <c r="F27" s="14" t="n">
         <v>98</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="G27" s="14" t="n">
         <v>52</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="H27" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="I27" s="13" t="n">
+      <c r="I27" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="J27" s="13" t="n">
+      <c r="J27" s="14" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2643,28 +2801,28 @@
           <t>短期入所生活介護</t>
         </is>
       </c>
-      <c r="C28" s="12" t="n">
+      <c r="C28" s="13" t="n">
         <v>26.5</v>
       </c>
-      <c r="D28" s="12" t="n">
+      <c r="D28" s="13" t="n">
         <v>0.583</v>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="E28" s="13" t="n">
         <v>0.917</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="F28" s="13" t="n">
         <v>6.417</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="G28" s="13" t="n">
         <v>10.417</v>
       </c>
-      <c r="H28" s="12" t="n">
+      <c r="H28" s="13" t="n">
         <v>3.417</v>
       </c>
-      <c r="I28" s="12" t="n">
+      <c r="I28" s="13" t="n">
         <v>3.5</v>
       </c>
-      <c r="J28" s="12" t="n">
+      <c r="J28" s="13" t="n">
         <v>1.25</v>
       </c>
     </row>
@@ -2675,28 +2833,28 @@
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr"/>
-      <c r="C29" s="13" t="n">
+      <c r="C29" s="14" t="n">
         <v>26</v>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E29" s="13" t="n">
+      <c r="E29" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="13" t="n">
+      <c r="F29" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="G29" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="H29" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="I29" s="13" t="n">
+      <c r="I29" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="J29" s="13" t="n">
+      <c r="J29" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2711,28 +2869,28 @@
           <t>短期入所療養介護（老健）</t>
         </is>
       </c>
-      <c r="C30" s="12" t="n">
+      <c r="C30" s="13" t="n">
         <v>16.583</v>
       </c>
-      <c r="D30" s="12" t="n">
+      <c r="D30" s="13" t="n">
         <v>0.417</v>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="13" t="n">
         <v>0.083</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="F30" s="13" t="n">
         <v>2.833</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="G30" s="13" t="n">
         <v>5.167</v>
       </c>
-      <c r="H30" s="12" t="n">
+      <c r="H30" s="13" t="n">
         <v>2.75</v>
       </c>
-      <c r="I30" s="12" t="n">
+      <c r="I30" s="13" t="n">
         <v>4.167</v>
       </c>
-      <c r="J30" s="12" t="n">
+      <c r="J30" s="13" t="n">
         <v>1.167</v>
       </c>
     </row>
@@ -2743,28 +2901,28 @@
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr"/>
-      <c r="C31" s="13" t="n">
+      <c r="C31" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="D31" s="13" t="n">
+      <c r="D31" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="13" t="n">
+      <c r="E31" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="G31" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="H31" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="I31" s="13" t="n">
+      <c r="I31" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="J31" s="13" t="n">
+      <c r="J31" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2779,28 +2937,28 @@
           <t>福祉用具貸与</t>
         </is>
       </c>
-      <c r="C32" s="12" t="n">
+      <c r="C32" s="13" t="n">
         <v>642.083</v>
       </c>
-      <c r="D32" s="12" t="n">
+      <c r="D32" s="13" t="n">
         <v>66.25</v>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="E32" s="13" t="n">
         <v>118.75</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="F32" s="13" t="n">
         <v>177.5</v>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="G32" s="13" t="n">
         <v>123</v>
       </c>
-      <c r="H32" s="12" t="n">
+      <c r="H32" s="13" t="n">
         <v>65.917</v>
       </c>
-      <c r="I32" s="12" t="n">
+      <c r="I32" s="13" t="n">
         <v>49.667</v>
       </c>
-      <c r="J32" s="12" t="n">
+      <c r="J32" s="13" t="n">
         <v>41</v>
       </c>
     </row>
@@ -2811,28 +2969,28 @@
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr"/>
-      <c r="C33" s="13" t="n">
+      <c r="C33" s="14" t="n">
         <v>642</v>
       </c>
-      <c r="D33" s="13" t="n">
+      <c r="D33" s="14" t="n">
         <v>66</v>
       </c>
-      <c r="E33" s="13" t="n">
+      <c r="E33" s="14" t="n">
         <v>119</v>
       </c>
-      <c r="F33" s="13" t="n">
+      <c r="F33" s="14" t="n">
         <v>177</v>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="G33" s="14" t="n">
         <v>123</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="H33" s="14" t="n">
         <v>66</v>
       </c>
-      <c r="I33" s="13" t="n">
+      <c r="I33" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="J33" s="13" t="n">
+      <c r="J33" s="14" t="n">
         <v>41</v>
       </c>
     </row>
@@ -2847,28 +3005,28 @@
           <t>特定福祉用具購入費</t>
         </is>
       </c>
-      <c r="C34" s="12" t="n">
+      <c r="C34" s="13" t="n">
         <v>10.75</v>
       </c>
-      <c r="D34" s="12" t="n">
+      <c r="D34" s="13" t="n">
         <v>1.667</v>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="E34" s="13" t="n">
         <v>2.083</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="F34" s="13" t="n">
         <v>3.5</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="G34" s="13" t="n">
         <v>2.167</v>
       </c>
-      <c r="H34" s="12" t="n">
+      <c r="H34" s="13" t="n">
         <v>0.667</v>
       </c>
-      <c r="I34" s="12" t="n">
+      <c r="I34" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="J34" s="12" t="n">
+      <c r="J34" s="13" t="n">
         <v>0.167</v>
       </c>
     </row>
@@ -2879,28 +3037,28 @@
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr"/>
-      <c r="C35" s="13" t="n">
+      <c r="C35" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="D35" s="13" t="n">
+      <c r="D35" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="E35" s="13" t="n">
+      <c r="E35" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F35" s="13" t="n">
+      <c r="F35" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="G35" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="H35" s="13" t="n">
+      <c r="H35" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="I35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="13" t="n">
+      <c r="I35" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2915,28 +3073,28 @@
           <t>住宅改修費</t>
         </is>
       </c>
-      <c r="C36" s="12" t="n">
+      <c r="C36" s="13" t="n">
         <v>8.417</v>
       </c>
-      <c r="D36" s="12" t="n">
+      <c r="D36" s="13" t="n">
         <v>2.25</v>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="E36" s="13" t="n">
         <v>1.583</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="F36" s="13" t="n">
         <v>2.333</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="G36" s="13" t="n">
         <v>1.25</v>
       </c>
-      <c r="H36" s="12" t="n">
+      <c r="H36" s="13" t="n">
         <v>0.583</v>
       </c>
-      <c r="I36" s="12" t="n">
+      <c r="I36" s="13" t="n">
         <v>0.167</v>
       </c>
-      <c r="J36" s="12" t="n">
+      <c r="J36" s="13" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -2947,28 +3105,28 @@
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr"/>
-      <c r="C37" s="13" t="n">
+      <c r="C37" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="D37" s="13" t="n">
+      <c r="D37" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="E37" s="13" t="n">
+      <c r="E37" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F37" s="13" t="n">
+      <c r="F37" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="G37" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="13" t="n">
+      <c r="H37" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="I37" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="13" t="n">
+      <c r="I37" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2983,28 +3141,28 @@
           <t>介護予防支援・居宅介護支援</t>
         </is>
       </c>
-      <c r="C38" s="12" t="n">
+      <c r="C38" s="13" t="n">
         <v>913.333</v>
       </c>
-      <c r="D38" s="12" t="n">
+      <c r="D38" s="13" t="n">
         <v>100.25</v>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="13" t="n">
         <v>156.667</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="F38" s="13" t="n">
         <v>298.583</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="G38" s="13" t="n">
         <v>167.583</v>
       </c>
-      <c r="H38" s="12" t="n">
+      <c r="H38" s="13" t="n">
         <v>77.25</v>
       </c>
-      <c r="I38" s="12" t="n">
+      <c r="I38" s="13" t="n">
         <v>67.333</v>
       </c>
-      <c r="J38" s="12" t="n">
+      <c r="J38" s="13" t="n">
         <v>45.667</v>
       </c>
     </row>
@@ -3015,28 +3173,28 @@
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr"/>
-      <c r="C39" s="13" t="n">
+      <c r="C39" s="14" t="n">
         <v>913</v>
       </c>
-      <c r="D39" s="13" t="n">
+      <c r="D39" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="E39" s="13" t="n">
+      <c r="E39" s="14" t="n">
         <v>157</v>
       </c>
-      <c r="F39" s="13" t="n">
+      <c r="F39" s="14" t="n">
         <v>298</v>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="G39" s="14" t="n">
         <v>168</v>
       </c>
-      <c r="H39" s="13" t="n">
+      <c r="H39" s="14" t="n">
         <v>77</v>
       </c>
-      <c r="I39" s="13" t="n">
+      <c r="I39" s="14" t="n">
         <v>67</v>
       </c>
-      <c r="J39" s="13" t="n">
+      <c r="J39" s="14" t="n">
         <v>46</v>
       </c>
     </row>
@@ -3051,28 +3209,28 @@
           <t>定期巡回・随時対応型訪問介護看護</t>
         </is>
       </c>
-      <c r="C40" s="12" t="n">
+      <c r="C40" s="13" t="n">
         <v>0.583</v>
       </c>
-      <c r="D40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="12" t="n">
+      <c r="D40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="13" t="n">
         <v>0.25</v>
       </c>
-      <c r="G40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="12" t="n">
+      <c r="G40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="13" t="n">
         <v>0.333</v>
       </c>
     </row>
@@ -3083,28 +3241,28 @@
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr"/>
-      <c r="C41" s="13" t="n">
+      <c r="C41" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="13" t="n">
+      <c r="D41" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3119,28 +3277,28 @@
           <t>地域密着型通所介護</t>
         </is>
       </c>
-      <c r="C42" s="12" t="n">
+      <c r="C42" s="13" t="n">
         <v>76.167</v>
       </c>
-      <c r="D42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="12" t="n">
+      <c r="D42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="13" t="n">
         <v>37.083</v>
       </c>
-      <c r="G42" s="12" t="n">
+      <c r="G42" s="13" t="n">
         <v>23.583</v>
       </c>
-      <c r="H42" s="12" t="n">
+      <c r="H42" s="13" t="n">
         <v>8.667</v>
       </c>
-      <c r="I42" s="12" t="n">
+      <c r="I42" s="13" t="n">
         <v>3.833</v>
       </c>
-      <c r="J42" s="12" t="n">
+      <c r="J42" s="13" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3151,28 +3309,28 @@
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr"/>
-      <c r="C43" s="13" t="n">
+      <c r="C43" s="14" t="n">
         <v>76</v>
       </c>
-      <c r="D43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="13" t="n">
+      <c r="D43" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="14" t="n">
         <v>37</v>
       </c>
-      <c r="G43" s="13" t="n">
+      <c r="G43" s="14" t="n">
         <v>23</v>
       </c>
-      <c r="H43" s="13" t="n">
+      <c r="H43" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="I43" s="13" t="n">
+      <c r="I43" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="J43" s="13" t="n">
+      <c r="J43" s="14" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3187,28 +3345,28 @@
           <t>認知症対応型通所介護</t>
         </is>
       </c>
-      <c r="C44" s="12" t="n">
+      <c r="C44" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="12" t="n">
+      <c r="D44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="12" t="n">
+      <c r="H44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3219,28 +3377,28 @@
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr"/>
-      <c r="C45" s="13" t="n">
+      <c r="C45" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="13" t="n">
+      <c r="D45" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="13" t="n">
+      <c r="H45" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3255,28 +3413,28 @@
           <t>小規模多機能型居宅介護</t>
         </is>
       </c>
-      <c r="C46" s="12" t="n">
+      <c r="C46" s="13" t="n">
         <v>99.917</v>
       </c>
-      <c r="D46" s="12" t="n">
+      <c r="D46" s="13" t="n">
         <v>4.167</v>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="E46" s="13" t="n">
         <v>9.333</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="F46" s="13" t="n">
         <v>37.75</v>
       </c>
-      <c r="G46" s="12" t="n">
+      <c r="G46" s="13" t="n">
         <v>23.083</v>
       </c>
-      <c r="H46" s="12" t="n">
+      <c r="H46" s="13" t="n">
         <v>17.167</v>
       </c>
-      <c r="I46" s="12" t="n">
+      <c r="I46" s="13" t="n">
         <v>3.333</v>
       </c>
-      <c r="J46" s="12" t="n">
+      <c r="J46" s="13" t="n">
         <v>5.083</v>
       </c>
     </row>
@@ -3287,36 +3445,36 @@
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr"/>
-      <c r="C47" s="13" t="n">
+      <c r="C47" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="D47" s="13" t="n">
+      <c r="D47" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="E47" s="13" t="n">
+      <c r="E47" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="F47" s="13" t="n">
+      <c r="F47" s="14" t="n">
         <v>38</v>
       </c>
-      <c r="G47" s="13" t="n">
+      <c r="G47" s="14" t="n">
         <v>23</v>
       </c>
-      <c r="H47" s="13" t="n">
+      <c r="H47" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="I47" s="13" t="n">
+      <c r="I47" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="J47" s="13" t="n">
+      <c r="J47" s="14" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="49" ht="56" customHeight="1">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>注2）★の行（小数）が入力値です。
-注3）整数に丸めると0又は1になるサービスが2件あります（定期巡回・随時対応型訪問介護看護・認知症対応型通所介護）。0を入れると令和9年度から令和11年度も0のまま残るため、小数で入力できるかをご確認ください。定期巡回・随時対応型訪問介護看護は要介護1が3人・要介護5が4人（いずれも年間の延べ人数）で、整数に丸めると要介護1が0、要介護5が0となります。
+          <t>注2）人数の欄は整数で扱われるため、下段の「（整数）」が入力値です（00シート3参照）。
+注3）整数に丸めると計が0又は1になるサービスが2件あります（定期巡回・随時対応型訪問介護看護・認知症対応型通所介護）。群ごとに合計を保つ丸め方によるため、定期巡回・随時対応型訪問介護看護（月0.583人）は要介護5に1人が立ち、0にはなりません。各欄を単純に四捨五入すると全欄が0になり、令和9年度から令和11年度も0のまま残ります。
 注4）区域内に事業所がなく実績もないサービス（夜間対応型訪問介護・看護小規模多機能型居宅介護・短期入所療養介護（病院等）・短期入所療養介護（介護医療院）・登録施設介護支援）は年報の値が0であるため本表に載せていません。画面にある場合は0を入れます。
 注5）要支援の欄が0のサービスが6件あります（訪問介護・訪問入浴介護・通所介護・定期巡回・随時対応型訪問介護看護・地域密着型通所介護・認知症対応型通所介護）。予防給付が総合事業へ移行したもの（訪問介護・通所介護）と、予防給付の区分がないもの（地域密着型通所介護）です。</t>
         </is>
@@ -3341,7 +3499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3427,130 +3585,140 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
+          <t>（実数）</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>14965.083</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>2356.75</v>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>1815</v>
+      </c>
+      <c r="I5" s="16" t="n">
+        <v>2880.167</v>
+      </c>
+      <c r="J5" s="16" t="n">
+        <v>4122.5</v>
+      </c>
+      <c r="K5" s="16" t="n">
+        <v>3790.667</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
           <t>★</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>訪問介護</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>回</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>14965.083</v>
-      </c>
-      <c r="E5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>2356.75</v>
-      </c>
-      <c r="H5" s="12" t="n">
-        <v>1815</v>
-      </c>
-      <c r="I5" s="12" t="n">
-        <v>2880.167</v>
-      </c>
-      <c r="J5" s="12" t="n">
-        <v>4122.5</v>
-      </c>
-      <c r="K5" s="12" t="n">
-        <v>3790.667</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>（2区分）</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr"/>
       <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="15" t="n">
-        <v>14965.083</v>
-      </c>
-      <c r="E6" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" s="17" t="n">
-        <v>14965.083</v>
-      </c>
-      <c r="J6" s="6" t="inlineStr"/>
-      <c r="K6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="20" customHeight="1">
+      <c r="D6" s="18" t="n">
+        <v>14965.1</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>2356.7</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>1815</v>
+      </c>
+      <c r="I6" s="18" t="n">
+        <v>2880.2</v>
+      </c>
+      <c r="J6" s="18" t="n">
+        <v>4122.5</v>
+      </c>
+      <c r="K6" s="18" t="n">
+        <v>3790.7</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
+          <t>（2区分）</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="19" t="n">
+        <v>14965.1</v>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="20" t="n">
+        <v>14965.1</v>
+      </c>
+      <c r="J7" s="6" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>（実数）</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>訪問入浴介護</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>回</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D8" s="16" t="n">
         <v>33</v>
       </c>
-      <c r="E7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="12" t="n">
+      <c r="E8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="16" t="n">
         <v>8.583</v>
       </c>
-      <c r="H7" s="12" t="n">
+      <c r="H8" s="16" t="n">
         <v>0.917</v>
       </c>
-      <c r="I7" s="12" t="n">
+      <c r="I8" s="16" t="n">
         <v>0.833</v>
       </c>
-      <c r="J7" s="12" t="n">
+      <c r="J8" s="16" t="n">
         <v>4.75</v>
       </c>
-      <c r="K7" s="12" t="n">
+      <c r="K8" s="16" t="n">
         <v>17.917</v>
       </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>（2区分）</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr"/>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="15" t="n">
-        <v>33</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="17" t="n">
-        <v>33</v>
-      </c>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
@@ -3558,39 +3726,31 @@
           <t>★</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>訪問看護</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>回</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>1076</v>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>39.583</v>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>244.5</v>
-      </c>
-      <c r="H9" s="12" t="n">
-        <v>178.917</v>
-      </c>
-      <c r="I9" s="12" t="n">
-        <v>110.083</v>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>197.083</v>
-      </c>
-      <c r="K9" s="12" t="n">
-        <v>241.833</v>
+      <c r="B9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="18" t="n">
+        <v>33</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K9" s="18" t="n">
+        <v>17.9</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -3601,17 +3761,17 @@
       </c>
       <c r="B10" s="6" t="inlineStr"/>
       <c r="C10" s="6" t="inlineStr"/>
-      <c r="D10" s="15" t="n">
-        <v>1076</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>103.583</v>
+      <c r="D10" s="19" t="n">
+        <v>33</v>
+      </c>
+      <c r="E10" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="6" t="inlineStr"/>
       <c r="G10" s="6" t="inlineStr"/>
       <c r="H10" s="6" t="inlineStr"/>
-      <c r="I10" s="17" t="n">
-        <v>972.417</v>
+      <c r="I10" s="20" t="n">
+        <v>33</v>
       </c>
       <c r="J10" s="6" t="inlineStr"/>
       <c r="K10" s="6" t="inlineStr"/>
@@ -3619,130 +3779,140 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
+          <t>（実数）</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>訪問看護</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>1076</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>39.583</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>64</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>244.5</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <v>178.917</v>
+      </c>
+      <c r="I11" s="16" t="n">
+        <v>110.083</v>
+      </c>
+      <c r="J11" s="16" t="n">
+        <v>197.083</v>
+      </c>
+      <c r="K11" s="16" t="n">
+        <v>241.833</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
           <t>★</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>訪問リハビリテーション</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>回</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>764.667</v>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="F11" s="12" t="n">
-        <v>116.333</v>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>207.917</v>
-      </c>
-      <c r="H11" s="12" t="n">
-        <v>208.917</v>
-      </c>
-      <c r="I11" s="12" t="n">
-        <v>111</v>
-      </c>
-      <c r="J11" s="12" t="n">
-        <v>39.583</v>
-      </c>
-      <c r="K11" s="12" t="n">
-        <v>56.917</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>（2区分）</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr"/>
       <c r="C12" s="6" t="inlineStr"/>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="18" t="n">
+        <v>1076</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>64</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>244.5</v>
+      </c>
+      <c r="H12" s="18" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>197.1</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>241.8</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>（2区分）</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="inlineStr"/>
+      <c r="D13" s="19" t="n">
+        <v>1076</v>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr"/>
+      <c r="G13" s="6" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr"/>
+      <c r="I13" s="20" t="n">
+        <v>972.4</v>
+      </c>
+      <c r="J13" s="6" t="inlineStr"/>
+      <c r="K13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>（実数）</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>訪問リハビリテーション</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="n">
         <v>764.667</v>
       </c>
-      <c r="E12" s="17" t="n">
-        <v>140.333</v>
-      </c>
-      <c r="F12" s="6" t="inlineStr"/>
-      <c r="G12" s="6" t="inlineStr"/>
-      <c r="H12" s="6" t="inlineStr"/>
-      <c r="I12" s="17" t="n">
-        <v>624.333</v>
-      </c>
-      <c r="J12" s="6" t="inlineStr"/>
-      <c r="K12" s="6" t="inlineStr"/>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>通所介護</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>回</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>850.583</v>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="12" t="n">
-        <v>417.167</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>164.75</v>
-      </c>
-      <c r="I13" s="12" t="n">
-        <v>107.833</v>
-      </c>
-      <c r="J13" s="12" t="n">
-        <v>130.75</v>
-      </c>
-      <c r="K13" s="12" t="n">
-        <v>30.083</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>（2区分）</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr"/>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="15" t="n">
-        <v>850.583</v>
-      </c>
-      <c r="E14" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="17" t="n">
-        <v>850.583</v>
-      </c>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="E14" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>116.333</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <v>207.917</v>
+      </c>
+      <c r="H14" s="16" t="n">
+        <v>208.917</v>
+      </c>
+      <c r="I14" s="16" t="n">
+        <v>111</v>
+      </c>
+      <c r="J14" s="16" t="n">
+        <v>39.583</v>
+      </c>
+      <c r="K14" s="16" t="n">
+        <v>56.917</v>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
@@ -3750,39 +3920,31 @@
           <t>★</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>通所リハビリテーション</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>回</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="n">
-        <v>1354</v>
-      </c>
-      <c r="E15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>647.833</v>
-      </c>
-      <c r="H15" s="12" t="n">
-        <v>398.167</v>
-      </c>
-      <c r="I15" s="12" t="n">
-        <v>160.333</v>
-      </c>
-      <c r="J15" s="12" t="n">
-        <v>102.083</v>
-      </c>
-      <c r="K15" s="12" t="n">
-        <v>45.583</v>
+      <c r="B15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="18" t="n">
+        <v>764.6</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>24</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>207.9</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>208.9</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>111</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="K15" s="18" t="n">
+        <v>56.9</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -3793,17 +3955,17 @@
       </c>
       <c r="B16" s="6" t="inlineStr"/>
       <c r="C16" s="6" t="inlineStr"/>
-      <c r="D16" s="15" t="n">
-        <v>1354</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>0</v>
+      <c r="D16" s="19" t="n">
+        <v>764.6</v>
+      </c>
+      <c r="E16" s="20" t="n">
+        <v>140.3</v>
       </c>
       <c r="F16" s="6" t="inlineStr"/>
       <c r="G16" s="6" t="inlineStr"/>
       <c r="H16" s="6" t="inlineStr"/>
-      <c r="I16" s="17" t="n">
-        <v>1354</v>
+      <c r="I16" s="20" t="n">
+        <v>624.3</v>
       </c>
       <c r="J16" s="6" t="inlineStr"/>
       <c r="K16" s="6" t="inlineStr"/>
@@ -3811,130 +3973,140 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
+          <t>（実数）</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>通所介護</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="n">
+        <v>850.583</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>417.167</v>
+      </c>
+      <c r="H17" s="16" t="n">
+        <v>164.75</v>
+      </c>
+      <c r="I17" s="16" t="n">
+        <v>107.833</v>
+      </c>
+      <c r="J17" s="16" t="n">
+        <v>130.75</v>
+      </c>
+      <c r="K17" s="16" t="n">
+        <v>30.083</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
           <t>★</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>短期入所生活介護</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="n">
-        <v>306.167</v>
-      </c>
-      <c r="E17" s="12" t="n">
-        <v>2.083</v>
-      </c>
-      <c r="F17" s="12" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="G17" s="12" t="n">
-        <v>76.167</v>
-      </c>
-      <c r="H17" s="12" t="n">
-        <v>112.833</v>
-      </c>
-      <c r="I17" s="12" t="n">
-        <v>57.083</v>
-      </c>
-      <c r="J17" s="12" t="n">
-        <v>34.167</v>
-      </c>
-      <c r="K17" s="12" t="n">
-        <v>14.083</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>（2区分）</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr"/>
       <c r="C18" s="6" t="inlineStr"/>
-      <c r="D18" s="15" t="n">
-        <v>306.167</v>
-      </c>
-      <c r="E18" s="17" t="n">
-        <v>11.833</v>
-      </c>
-      <c r="F18" s="6" t="inlineStr"/>
-      <c r="G18" s="6" t="inlineStr"/>
-      <c r="H18" s="6" t="inlineStr"/>
-      <c r="I18" s="17" t="n">
-        <v>294.333</v>
-      </c>
-      <c r="J18" s="6" t="inlineStr"/>
-      <c r="K18" s="6" t="inlineStr"/>
-    </row>
-    <row r="19" ht="20" customHeight="1">
+      <c r="D18" s="18" t="n">
+        <v>850.6</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="18" t="n">
+        <v>417.2</v>
+      </c>
+      <c r="H18" s="18" t="n">
+        <v>164.8</v>
+      </c>
+      <c r="I18" s="18" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="J18" s="18" t="n">
+        <v>130.7</v>
+      </c>
+      <c r="K18" s="18" t="n">
+        <v>30.1</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>短期入所療養介護（老健）</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>日</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="n">
-        <v>100.5</v>
-      </c>
-      <c r="E19" s="12" t="n">
-        <v>1.583</v>
-      </c>
-      <c r="F19" s="12" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="G19" s="12" t="n">
-        <v>11.333</v>
-      </c>
-      <c r="H19" s="12" t="n">
-        <v>26.333</v>
-      </c>
-      <c r="I19" s="12" t="n">
-        <v>19.75</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>35.417</v>
-      </c>
-      <c r="K19" s="12" t="n">
-        <v>5.917</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
+          <t>（2区分）</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="inlineStr"/>
+      <c r="D19" s="19" t="n">
+        <v>850.6</v>
+      </c>
+      <c r="E19" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="inlineStr"/>
+      <c r="H19" s="6" t="inlineStr"/>
+      <c r="I19" s="20" t="n">
+        <v>850.6</v>
+      </c>
+      <c r="J19" s="6" t="inlineStr"/>
+      <c r="K19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>（2区分）</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr"/>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="15" t="n">
-        <v>100.5</v>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="17" t="n">
-        <v>98.75</v>
-      </c>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+          <t>（実数）</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>通所リハビリテーション</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="n">
+        <v>1354</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="16" t="n">
+        <v>647.833</v>
+      </c>
+      <c r="H20" s="16" t="n">
+        <v>398.167</v>
+      </c>
+      <c r="I20" s="16" t="n">
+        <v>160.333</v>
+      </c>
+      <c r="J20" s="16" t="n">
+        <v>102.083</v>
+      </c>
+      <c r="K20" s="16" t="n">
+        <v>45.583</v>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
@@ -3942,39 +4114,31 @@
           <t>★</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>地域密着型通所介護</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>回</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="n">
-        <v>600.667</v>
-      </c>
-      <c r="E21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="12" t="n">
-        <v>251.333</v>
-      </c>
-      <c r="H21" s="12" t="n">
-        <v>199.417</v>
-      </c>
-      <c r="I21" s="12" t="n">
-        <v>84.417</v>
-      </c>
-      <c r="J21" s="12" t="n">
-        <v>40.917</v>
-      </c>
-      <c r="K21" s="12" t="n">
-        <v>24.583</v>
+      <c r="B21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="18" t="n">
+        <v>1354</v>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="18" t="n">
+        <v>647.8</v>
+      </c>
+      <c r="H21" s="18" t="n">
+        <v>398.2</v>
+      </c>
+      <c r="I21" s="18" t="n">
+        <v>160.3</v>
+      </c>
+      <c r="J21" s="18" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="K21" s="18" t="n">
+        <v>45.6</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -3985,17 +4149,17 @@
       </c>
       <c r="B22" s="6" t="inlineStr"/>
       <c r="C22" s="6" t="inlineStr"/>
-      <c r="D22" s="15" t="n">
-        <v>600.667</v>
-      </c>
-      <c r="E22" s="17" t="n">
+      <c r="D22" s="19" t="n">
+        <v>1354</v>
+      </c>
+      <c r="E22" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="6" t="inlineStr"/>
       <c r="G22" s="6" t="inlineStr"/>
       <c r="H22" s="6" t="inlineStr"/>
-      <c r="I22" s="17" t="n">
-        <v>600.667</v>
+      <c r="I22" s="20" t="n">
+        <v>1354</v>
       </c>
       <c r="J22" s="6" t="inlineStr"/>
       <c r="K22" s="6" t="inlineStr"/>
@@ -4003,71 +4167,395 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
+          <t>（実数）</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>短期入所生活介護</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="n">
+        <v>306.167</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>2.083</v>
+      </c>
+      <c r="F23" s="16" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="G23" s="16" t="n">
+        <v>76.167</v>
+      </c>
+      <c r="H23" s="16" t="n">
+        <v>112.833</v>
+      </c>
+      <c r="I23" s="16" t="n">
+        <v>57.083</v>
+      </c>
+      <c r="J23" s="16" t="n">
+        <v>34.167</v>
+      </c>
+      <c r="K23" s="16" t="n">
+        <v>14.083</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
           <t>★</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>認知症対応型通所介護</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>回</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="n">
-        <v>7.917</v>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="12" t="n">
-        <v>7.917</v>
-      </c>
-      <c r="I23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>（2区分）</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr"/>
       <c r="C24" s="6" t="inlineStr"/>
-      <c r="D24" s="15" t="n">
+      <c r="D24" s="18" t="n">
+        <v>306.1</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G24" s="18" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="H24" s="18" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="I24" s="18" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J24" s="18" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="K24" s="18" t="n">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>（2区分）</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="inlineStr"/>
+      <c r="D25" s="19" t="n">
+        <v>306.1</v>
+      </c>
+      <c r="E25" s="20" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr"/>
+      <c r="G25" s="6" t="inlineStr"/>
+      <c r="H25" s="6" t="inlineStr"/>
+      <c r="I25" s="20" t="n">
+        <v>294.3</v>
+      </c>
+      <c r="J25" s="6" t="inlineStr"/>
+      <c r="K25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>（実数）</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>短期入所療養介護（老健）</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>1.583</v>
+      </c>
+      <c r="F26" s="16" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="G26" s="16" t="n">
+        <v>11.333</v>
+      </c>
+      <c r="H26" s="16" t="n">
+        <v>26.333</v>
+      </c>
+      <c r="I26" s="16" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="J26" s="16" t="n">
+        <v>35.417</v>
+      </c>
+      <c r="K26" s="16" t="n">
+        <v>5.917</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="inlineStr"/>
+      <c r="D27" s="18" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G27" s="18" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H27" s="18" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="I27" s="18" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="J27" s="18" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="K27" s="18" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>（2区分）</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr"/>
+      <c r="C28" s="6" t="inlineStr"/>
+      <c r="D28" s="19" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="E28" s="20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr"/>
+      <c r="G28" s="6" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr"/>
+      <c r="I28" s="20" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="J28" s="6" t="inlineStr"/>
+      <c r="K28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>（実数）</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型通所介護</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="n">
+        <v>600.667</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="16" t="n">
+        <v>251.333</v>
+      </c>
+      <c r="H29" s="16" t="n">
+        <v>199.417</v>
+      </c>
+      <c r="I29" s="16" t="n">
+        <v>84.417</v>
+      </c>
+      <c r="J29" s="16" t="n">
+        <v>40.917</v>
+      </c>
+      <c r="K29" s="16" t="n">
+        <v>24.583</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr"/>
+      <c r="C30" s="6" t="inlineStr"/>
+      <c r="D30" s="18" t="n">
+        <v>600.7</v>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="18" t="n">
+        <v>251.4</v>
+      </c>
+      <c r="H30" s="18" t="n">
+        <v>199.4</v>
+      </c>
+      <c r="I30" s="18" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="J30" s="18" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="K30" s="18" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>（2区分）</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="inlineStr"/>
+      <c r="D31" s="19" t="n">
+        <v>600.7</v>
+      </c>
+      <c r="E31" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="6" t="inlineStr"/>
+      <c r="G31" s="6" t="inlineStr"/>
+      <c r="H31" s="6" t="inlineStr"/>
+      <c r="I31" s="20" t="n">
+        <v>600.7</v>
+      </c>
+      <c r="J31" s="6" t="inlineStr"/>
+      <c r="K31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>（実数）</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型通所介護</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="n">
         <v>7.917</v>
       </c>
-      <c r="E24" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="6" t="inlineStr"/>
-      <c r="G24" s="6" t="inlineStr"/>
-      <c r="H24" s="6" t="inlineStr"/>
-      <c r="I24" s="17" t="n">
+      <c r="E32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="16" t="n">
         <v>7.917</v>
       </c>
-      <c r="J24" s="6" t="inlineStr"/>
-      <c r="K24" s="6" t="inlineStr"/>
-    </row>
-    <row r="26" ht="42" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>注1）★の行（小数）が入力値です。下段の「（2区分）」は、要支援1の位置に要支援計、要介護3の位置に要介護計を置いたものです。
+      <c r="I32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="inlineStr"/>
+      <c r="D33" s="18" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="18" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="I33" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>（2区分）</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr"/>
+      <c r="C34" s="6" t="inlineStr"/>
+      <c r="D34" s="19" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="E34" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="6" t="inlineStr"/>
+      <c r="G34" s="6" t="inlineStr"/>
+      <c r="H34" s="6" t="inlineStr"/>
+      <c r="I34" s="20" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J34" s="6" t="inlineStr"/>
+      <c r="K34" s="6" t="inlineStr"/>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>注1）★の行（小数第1位）が入力値です。利用回（日）数の欄は小数第1位まで受け付けます（05シート1参照）。丸めは群（要支援・要介護）ごとに合計を保つ最大剰余法によります。上段の「（実数）」は年報の値を12で除したそのままの値です。下段の「（2区分）」は、要支援1の位置に要支援計、要介護3の位置に要介護計を置いたものです。
 注2）要支援の欄が0のサービスは、予防給付が総合事業へ移行したもの（訪問介護・通所介護）、予防給付の区分がないもの（地域密着型通所介護・認知症対応型通所介護は要支援の実績が0）、月を単位とする報酬で回（日）数を持たないもの（介護予防通所リハビリテーションは受給者83人／月に対し利用回数が0）です。
 注3）本表は現物給付分です。様式2の審査決定件数（償還払いを含む）とは値が異なります。</t>
         </is>
@@ -4077,7 +4565,7 @@
   <mergeCells count="3">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="A36:K36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4089,7 +4577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4103,21 +4591,21 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>出所の突合と本表の限界</t>
+          <t>入力欄の桁・出所の突合・本表の限界</t>
         </is>
       </c>
     </row>
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>年報の要介護度別を12で除した月平均が見える化システムの総括表詳細（１）と一致することを確かめ、画面に表示された令和7年度の整数との食い違いを示す。</t>
+          <t>入力欄が小数をどこまで受け付けるかを確かめたうえで、年報の要介護度別を12で除した月平均が見える化システムの総括表詳細（１）と一致することを確かめ、画面に表示された令和7年度の整数との食い違いを示す。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　施設・居住系　画面の令和7年度・年報÷12・総括表÷12</t>
+          <t>1　入力欄が受け付ける桁（確認事項No.135の回答）</t>
         </is>
       </c>
     </row>
@@ -4125,200 +4613,303 @@
       <c r="A5" s="4" t="inlineStr"/>
       <c r="B5" s="4" t="inlineStr">
         <is>
+          <t>欄</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>実績（令和6・7年度）</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>実績見込み（令和8年度）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>推計（令和9〜11年度）</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>本表で用意するもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>利用者数（人数）</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>小数（÷12の値のまま）</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>すべて整数</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>すべて整数</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>整数版（02・03シートの下段）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>利用回（日）数</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>小数</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>小数第1位まで</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>小数第1位まで</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>小数第1位版（04シートの★の行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>注1）弊社の別案件において、令和8年度の実績見込み値を編集し小数を入力したうえで出力された推計結果により確かめたものです。同じ表の中で令和6・7年度の人数は小数10桁まで表示されるのに対し、編集した令和8年度の人数は全45サービスが整数、令和9年度から令和11年度の人数も全135件が整数でした。利用回（日）数は令和8年度・令和9年度以降とも小数第1位まで出ています。その保険者の数値は用いていません。
+注2）したがって、人数については「小数で入力できるか」ではなく「整数に丸めたときに小口が消えないか」が論点になります。本表の整数版は群（要支援・要介護）ごとに合計を保つため、定期巡回・随時対応型訪問介護看護は要介護5に1人が立ちます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2　施設・居住系　画面の令和7年度・年報÷12・総括表÷12</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="4" t="inlineStr"/>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
           <t>サービス</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>画面 令和7年度</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>年報÷12</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>画面との差</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>総括表÷12との突合</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="6" t="inlineStr"/>
-      <c r="B6" s="6" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="6" t="inlineStr"/>
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>特定施設入居者生活介護</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C13" s="5" t="n">
         <v>64</v>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D13" s="16" t="n">
         <v>61.5</v>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>+4.1%</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>一致（61.500）</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="6" t="inlineStr"/>
-      <c r="B7" s="6" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="6" t="inlineStr"/>
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>認知症対応型共同生活介護</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C14" s="5" t="n">
         <v>82</v>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D14" s="16" t="n">
         <v>81.583</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>+0.5%</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>一致（81.583）</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="6" t="inlineStr"/>
-      <c r="B8" s="6" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="6" t="inlineStr"/>
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>地域密着型特定施設入居者生活介護</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>一致（0.000）</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="6" t="inlineStr"/>
-      <c r="B9" s="6" t="inlineStr">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="6" t="inlineStr"/>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>地域密着型介護老人福祉施設入所者生活介護</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C16" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D16" s="16" t="n">
         <v>59.25</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>+1.3%</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>一致（59.250）</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="6" t="inlineStr"/>
-      <c r="B10" s="6" t="inlineStr">
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="6" t="inlineStr"/>
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>介護老人福祉施設</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C17" s="5" t="n">
         <v>140</v>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D17" s="16" t="n">
         <v>138.25</v>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>+1.3%</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>一致（138.250）</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="6" t="inlineStr"/>
-      <c r="B11" s="6" t="inlineStr">
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="6" t="inlineStr"/>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>介護老人保健施設</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C18" s="5" t="n">
         <v>130</v>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D18" s="16" t="n">
         <v>134.083</v>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>-3.0%</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>一致（134.083）</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="6" t="inlineStr"/>
-      <c r="B12" s="6" t="inlineStr">
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="6" t="inlineStr"/>
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>介護医療院</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C19" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D19" s="16" t="n">
         <v>5.5</v>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>+9.1%</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>一致（5.500）</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>注1）画面の整数と2％以上の差があるのは3件（特定施設入居者生活介護・介護老人保健施設・介護医療院）です。
 注2）年報の要介護度別を12で除した月平均は総括表詳細（１）の令和7年度と一致します。総括表詳細（１）の利用者数に総括表詳細（４）の1人1月あたり給付費を乗じると総括表詳細（５）の給付費になり、その合計は年報の給付費と円単位で一致します（令和7年度 2,915,307,125円）。年報・総括表・給付費が一つの系列でつながっています。
@@ -4326,175 +4917,62 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>2　本表の限界</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="4" t="inlineStr"/>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>限界</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>影響</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>解消する方法</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>画面の令和7年度との食い違いを説明できない</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>特定施設入居者生活介護で＋4.1％、介護老人保健施設で▲3.0％、介護医療院で＋9.1％の差がある。年報の側は要介護度別の和・総括表・給付費の三つで内的整合が取れている</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>見える化システム側の作り方のご確認（確認事項No.136）</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr"/>
-      <c r="F18" s="6" t="inlineStr"/>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>令和8年度が実際に減っているかを分けられない</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>介護老人保健施設は令和7年度から令和8年度へ14.6％減っている。季節の効き（施設は冬季が2.80％高い）では説明できない。実際の減少であれば令和7年度を置くと過大になる</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>休止床・改修・職員の状況のご確認（確認事項No.133）</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>入力欄が小数を受け付けるかが分からない</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>整数に丸めると定期巡回・随時対応型訪問介護看護（月0.583人）と認知症対応型通所介護（月1.000人）が0又は1に落ちる</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>画面でのご確認（確認事項No.135）</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-    </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>令和8年度の月報との接続を検算していない</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>令和8年度の実績見込み値を置き換えるのであって、令和8年4月から7月までの月報そのものは変えない。画面が月報から再計算する作りであれば入力値が戻る可能性がある</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>入力後の画面の表示のご確認</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>第2号被保険者の扱いを画面側で確かめていない</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>②③④は第1号・第2号の総数である（第2号は介護老人保健施設に年間の延べ15人など）。画面が第1号のみを求める場合は値が異なる</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>画面の表示のご確認。年報から第1号のみの値も出せる</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr"/>
-      <c r="F22" s="6" t="inlineStr"/>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>3　在宅サービス　年報÷12と総括表÷12の突合</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="4" t="inlineStr"/>
-      <c r="B25" s="4" t="inlineStr">
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="4" t="inlineStr"/>
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>サービス</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>年報÷12</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>総括表÷12</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>差</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>出所</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="6" t="inlineStr"/>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="n">
+        <v>270.083</v>
+      </c>
+      <c r="D25" s="16" t="n">
+        <v>270.083</v>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>様式1の7</t>
         </is>
       </c>
     </row>
@@ -4502,14 +4980,14 @@
       <c r="A26" s="6" t="inlineStr"/>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>訪問介護</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="n">
-        <v>270.083</v>
-      </c>
-      <c r="D26" s="15" t="n">
-        <v>270.083</v>
+          <t>訪問入浴介護</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D26" s="16" t="n">
+        <v>5.25</v>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
@@ -4526,14 +5004,14 @@
       <c r="A27" s="6" t="inlineStr"/>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>訪問入浴介護</t>
-        </is>
-      </c>
-      <c r="C27" s="15" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="D27" s="15" t="n">
-        <v>5.25</v>
+          <t>訪問看護</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>135.167</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>135.167</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
@@ -4550,14 +5028,14 @@
       <c r="A28" s="6" t="inlineStr"/>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>訪問看護</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="n">
-        <v>135.167</v>
-      </c>
-      <c r="D28" s="15" t="n">
-        <v>135.167</v>
+          <t>訪問リハビリテーション</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="n">
+        <v>66.917</v>
+      </c>
+      <c r="D28" s="16" t="n">
+        <v>66.917</v>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
@@ -4574,14 +5052,14 @@
       <c r="A29" s="6" t="inlineStr"/>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>訪問リハビリテーション</t>
-        </is>
-      </c>
-      <c r="C29" s="15" t="n">
-        <v>66.917</v>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>66.917</v>
+          <t>居宅療養管理指導</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="n">
+        <v>193.25</v>
+      </c>
+      <c r="D29" s="16" t="n">
+        <v>193.25</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
@@ -4598,14 +5076,14 @@
       <c r="A30" s="6" t="inlineStr"/>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>居宅療養管理指導</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="n">
-        <v>193.25</v>
-      </c>
-      <c r="D30" s="15" t="n">
-        <v>193.25</v>
+          <t>通所介護</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="n">
+        <v>97.333</v>
+      </c>
+      <c r="D30" s="16" t="n">
+        <v>97.333</v>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
@@ -4622,14 +5100,14 @@
       <c r="A31" s="6" t="inlineStr"/>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>通所介護</t>
-        </is>
-      </c>
-      <c r="C31" s="15" t="n">
-        <v>97.333</v>
-      </c>
-      <c r="D31" s="15" t="n">
-        <v>97.333</v>
+          <t>通所リハビリテーション</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="n">
+        <v>273.25</v>
+      </c>
+      <c r="D31" s="16" t="n">
+        <v>273.25</v>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
@@ -4646,14 +5124,14 @@
       <c r="A32" s="6" t="inlineStr"/>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>通所リハビリテーション</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="n">
-        <v>273.25</v>
-      </c>
-      <c r="D32" s="15" t="n">
-        <v>273.25</v>
+          <t>短期入所生活介護</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D32" s="16" t="n">
+        <v>26.5</v>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
@@ -4670,14 +5148,14 @@
       <c r="A33" s="6" t="inlineStr"/>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>短期入所生活介護</t>
-        </is>
-      </c>
-      <c r="C33" s="15" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="D33" s="15" t="n">
-        <v>26.5</v>
+          <t>短期入所療養介護（老健）</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="n">
+        <v>16.583</v>
+      </c>
+      <c r="D33" s="16" t="n">
+        <v>16.583</v>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
@@ -4694,14 +5172,14 @@
       <c r="A34" s="6" t="inlineStr"/>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>短期入所療養介護（老健）</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="n">
-        <v>16.583</v>
-      </c>
-      <c r="D34" s="15" t="n">
-        <v>16.583</v>
+          <t>福祉用具貸与</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="n">
+        <v>642.083</v>
+      </c>
+      <c r="D34" s="16" t="n">
+        <v>642.083</v>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
@@ -4718,14 +5196,14 @@
       <c r="A35" s="6" t="inlineStr"/>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>福祉用具貸与</t>
-        </is>
-      </c>
-      <c r="C35" s="15" t="n">
-        <v>642.083</v>
-      </c>
-      <c r="D35" s="15" t="n">
-        <v>642.083</v>
+          <t>特定福祉用具購入費</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="D35" s="16" t="n">
+        <v>10.75</v>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
@@ -4734,7 +5212,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>様式1の7</t>
+          <t>様式2（件数）</t>
         </is>
       </c>
     </row>
@@ -4742,14 +5220,14 @@
       <c r="A36" s="6" t="inlineStr"/>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>特定福祉用具購入費</t>
-        </is>
-      </c>
-      <c r="C36" s="15" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="D36" s="15" t="n">
-        <v>10.75</v>
+          <t>住宅改修費</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="n">
+        <v>8.417</v>
+      </c>
+      <c r="D36" s="16" t="n">
+        <v>8.417</v>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
@@ -4766,14 +5244,14 @@
       <c r="A37" s="6" t="inlineStr"/>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>住宅改修費</t>
-        </is>
-      </c>
-      <c r="C37" s="15" t="n">
-        <v>8.417</v>
-      </c>
-      <c r="D37" s="15" t="n">
-        <v>8.417</v>
+          <t>介護予防支援・居宅介護支援</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="n">
+        <v>913.333</v>
+      </c>
+      <c r="D37" s="16" t="n">
+        <v>913.333</v>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
@@ -4782,7 +5260,7 @@
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>様式2（件数）</t>
+          <t>様式1の7</t>
         </is>
       </c>
     </row>
@@ -4790,14 +5268,14 @@
       <c r="A38" s="6" t="inlineStr"/>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>介護予防支援・居宅介護支援</t>
-        </is>
-      </c>
-      <c r="C38" s="15" t="n">
-        <v>913.333</v>
-      </c>
-      <c r="D38" s="15" t="n">
-        <v>913.333</v>
+          <t>定期巡回・随時対応型訪問介護看護</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="D38" s="16" t="n">
+        <v>0.583</v>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
@@ -4814,14 +5292,14 @@
       <c r="A39" s="6" t="inlineStr"/>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護</t>
-        </is>
-      </c>
-      <c r="C39" s="15" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="D39" s="15" t="n">
-        <v>0.583</v>
+          <t>地域密着型通所介護</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="n">
+        <v>76.167</v>
+      </c>
+      <c r="D39" s="16" t="n">
+        <v>76.167</v>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
@@ -4838,14 +5316,14 @@
       <c r="A40" s="6" t="inlineStr"/>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>地域密着型通所介護</t>
-        </is>
-      </c>
-      <c r="C40" s="15" t="n">
-        <v>76.167</v>
-      </c>
-      <c r="D40" s="15" t="n">
-        <v>76.167</v>
+          <t>認知症対応型通所介護</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="16" t="n">
+        <v>1</v>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
@@ -4862,58 +5340,151 @@
       <c r="A41" s="6" t="inlineStr"/>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型通所介護</t>
-        </is>
-      </c>
-      <c r="C41" s="15" t="n">
+          <t>小規模多機能型居宅介護</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="n">
+        <v>99.917</v>
+      </c>
+      <c r="D41" s="16" t="n">
+        <v>99.917</v>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>様式1の7</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>4　本表の限界</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="4" t="inlineStr"/>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>限界</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>影響</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>解消する方法</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45" ht="52" customHeight="1">
+      <c r="A45" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>一致</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>様式1の7</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="6" t="inlineStr"/>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>小規模多機能型居宅介護</t>
-        </is>
-      </c>
-      <c r="C42" s="15" t="n">
-        <v>99.917</v>
-      </c>
-      <c r="D42" s="15" t="n">
-        <v>99.917</v>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>一致</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>様式1の7</t>
-        </is>
-      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>画面の令和7年度との食い違いを説明できない</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>特定施設入居者生活介護で＋4.1％、介護老人保健施設で▲3.0％、介護医療院で＋9.1％の差がある。年報の側は要介護度別の和・総括表・給付費の三つで内的整合が取れている</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>見える化システム側の作り方のご確認（確認事項No.136）</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr"/>
+      <c r="F45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46" ht="52" customHeight="1">
+      <c r="A46" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度が実際に減っているかを分けられない</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>介護老人保健施設は令和7年度から令和8年度へ14.6％減っている。季節の効き（施設は冬季が2.80％高い）では説明できない。実際の減少であれば令和7年度を置くと過大になる</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>休止床・改修・職員の状況のご確認（確認事項No.133）</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr"/>
+      <c r="F46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47" ht="52" customHeight="1">
+      <c r="A47" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度の月報との接続を検算していない</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度の実績見込み値を置き換えるのであって、令和8年4月から7月までの月報そのものは変えない。画面が月報から再計算する作りであれば入力値が戻る可能性がある</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>入力後の画面の表示のご確認</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr"/>
+      <c r="F47" s="6" t="inlineStr"/>
+    </row>
+    <row r="48" ht="52" customHeight="1">
+      <c r="A48" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>第2号被保険者の扱いを画面側で確かめていない</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>②③④は第1号・第2号の総数である（第2号は介護老人保健施設に年間の延べ15人など）。画面が第1号のみを求める場合は値が異なる</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>画面の表示のご確認。年報から第1号のみの値も出せる</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr"/>
+      <c r="F48" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A24:F24"/>
+  <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A9:F9"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A43:F43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4925,7 +5496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5316,32 +5887,84 @@
       </c>
       <c r="F17" s="6" t="inlineStr"/>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="10" t="inlineStr"/>
-      <c r="B18" s="10" t="inlineStr">
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>整数版で実績のあるサービスが消えないこと</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>在宅17サービス</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>消えるものはない（定期巡回は月0.583人で要介護5に1人が立つ）</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>利用回（日）数の小数第1位版が群（要支援・要介護）ごとに実数と0.05を超えて離れないこと</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>10サービス×2群</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>全件0.05以内</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="11" t="inlineStr"/>
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>13件</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>適合13件・不適合0件</t>
-        </is>
-      </c>
-      <c r="E18" s="19" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>15件</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>適合15件・不適合0件</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr"/>
-    </row>
-    <row r="20" ht="56" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr"/>
+    </row>
+    <row r="22" ht="56" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>注1）点検2・3が本表の要です。年報の要介護度別を12で除して足した値が、見える化システムの総括表詳細（１）の令和7年度と施設・居住系7サービス・在宅17サービスのすべてで一致します（許容0.0005人）。年報と総括表が同じ系列であることが確かめられ、要介護度別の内訳を確定値として扱えます。
 注2）点検11は、④を③で除して1人1月あたりに戻したとき総括表詳細（３）と一致するかの点検です。④と③が同じ集計から出ていることを確かめています。
@@ -5352,8 +5975,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A20:F20"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5366,7 +5989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5463,27 +6086,27 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>入力欄が小数を受け付けるか</t>
+          <t>入力欄が小数を受け付けるか　→　解決</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>整数に丸めると0又は1になるサービスがある。定期巡回・随時対応型訪問介護看護は月平均0.583人、認知症対応型通所介護は月平均1.000人である。0を入れると令和9年度から令和11年度も0のまま残り、区域外の事業所による利用の実績が消える。①入力欄が小数を受け付けるかをご確認いただきたい。②整数しか受け付けない場合、定期巡回を0とするか1とするかをご判断いただきたい。当方は本表で最大剰余法により群の合計を保つ整数を用意している。</t>
+          <t>令和8年9月11日、弊社の別案件において実際に小数を入力して出力された推計結果により次を確かめた。①利用者数（人数）の欄は整数で扱われる（令和6・7年度の実績は小数10桁まで表示されるのに対し、編集した令和8年度の人数は全45サービスが整数、令和9年度から令和11年度の推計値も全135件が整数）。②利用回（日）数の欄は小数第1位まで受け付ける。本表は人数を整数版（群ごとに合計を保つ最大剰余法）、利用回（日）数を小数第1位版として用意した。定期巡回・随時対応型訪問介護看護（月0.583人）は要介護5に1人が立ち、0にはならない。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階</t>
+          <t>（解消済み）</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>―</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -5520,10 +6143,43 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>注1）本表に係る確認事項は3件（No.134〜No.136）で、うちNo.134は解消により取り下げます。ご確認をお願いするのはNo.135・No.136の2件です。
+    <row r="8" ht="150" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>No.137</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>「推計方法の設定」には、1人1月あたり給付費の実績値を令和7年度とするか令和8年度とするかを選ぶ項目があり、施設・居住系と在宅で別に選べる。①当方は令和7年度（12か月の完結年度）を選ぶ案としたい。②ただし当方の検証では、単価は介護報酬改定の有無に関係なく年率1.75％で伸びており（構成を固定した連鎖ラスパイレス指数で7年＋12.93％）、令和7年度で固定することは月額で＋185〜＋374円に当たる。③令和9年度は介護報酬改定の年である（3年周期。第10期の初年度）。改定率1％あたり月額＋61円である。④施設・居住系と在宅で年度をそろえるかどうかも併せてご判断いただきたい。</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>将来推計 第2段階
+サービス見込量 第1次概算</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>注1）本表に係る確認事項は4件（No.134〜No.137）で、うちNo.134は取下げ、No.135は解決しました。ご判断・ご確認をお願いするのはNo.136・No.137の2件です。
 注2）既に起票済みのNo.128（実績見込み値を編集するか）・No.132（在宅の編集画面の現在値）・No.133（介護老人保健施設の減少）とも関わります。No.132（在宅の編集画面の現在値のご提供）は、年報により入力値が確定したため、画面の並びに合わせるための参考にとどまります。
 注3）確認事項は業務工程管理表 03_確認事項一覧で一元管理します。</t>
         </is>
@@ -5533,7 +6189,7 @@
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx
+++ b/output/第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx
@@ -91,12 +91,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -155,13 +155,13 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -170,7 +170,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -185,7 +185,7 @@
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -200,7 +200,7 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -595,7 +595,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　差し替える4画面と出所</t>
+          <t>1　差し替える項目と出所</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,8 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>① 認定者数の実績値</t>
+          <t>① 認定者数の実績値
+［編集項目の有無を要確認］</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -643,7 +644,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>確定値</t>
+          <t>値は確定値。ただし編集する項目が画面にあるかを確かめられていない（確認事項No.138）</t>
         </is>
       </c>
     </row>
@@ -666,7 +667,7 @@
           <t>サービス別・要介護度別の月平均（02シート）</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>確定値</t>
         </is>
@@ -691,7 +692,7 @@
           <t>サービス別・要介護度別の月平均（03シート）</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>確定値</t>
         </is>
@@ -716,16 +717,16 @@
           <t>サービス別・要介護度別の月平均（04シート）</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>確定値</t>
         </is>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>注1）当方が先にお示ししたのは②③の2画面だけでした。①を差し替えないと利用率の分母が令和8年度のままになり、利用者数だけを令和7年度に置いても令和7年度の利用率になりません。
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>注1）②③④はそのまま入力していただけます。①については、当方が先に「4画面目」としてお示ししましたが、編集する項目が画面にあるかを確かめられていません（確認事項No.138）。受領した画面の写しで「実績及び推計方法の設定」に列挙されている編集項目は（3）1）施設・居住系の利用者数、（4）1）在宅の利用者数、（4）2）在宅の利用回（日）数の3件で、認定者数の実績見込み値を編集する項目は写っていません。また画面の認定率は令和7年度・令和8年度とも20.84％で同じであり、令和8年度は既に令和7年度の率で置かれている可能性があります。編集する項目がない場合は、認定率の伸びに「令和6年度→令和7年度の伸び」を選ぶことで令和8年度の影響を避ける形になります（本節3の④）。
 注2）令和8年9月11日に年報（令和7年度）の全様式を電子データで確認したことにより、②③④の要介護度別の内訳が按分による推定値ではなく確定値になりました（それ以前は在宅サービス利用率による按分でした）。要介護度別に合計して12で除した値が見える化システムの総括表詳細（１）の令和7年度と全サービスで一致することを06シートで検算しています。
 注3）年報は令和8年8月28日に受領済みの資料（資料No.22）と同一のものです。当方は主要値のみを取り込んでおり、サービス種別×要介護度の明細を取り込んでいませんでした。確認事項No.134は当方の取込漏れによるものであり、取り下げます。</t>
         </is>
@@ -856,7 +857,7 @@
           <t>利用者数（人数）の欄</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>整数版（02・03シートの下段）を入力する</t>
         </is>
@@ -877,7 +878,7 @@
           <t>利用回（日）数の欄</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>小数第1位版（04シートの★の行）を入力する</t>
         </is>
@@ -898,7 +899,7 @@
           <t>実績見込み値を編集した理由の記入欄</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>「令和8年度の実績が4か月分であるため」</t>
         </is>
@@ -919,7 +920,7 @@
           <t>認定率の伸び・利用率の伸びの選択</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>「当該市町村における令和6年度→令和7年度の伸び」を選ぶ</t>
         </is>
@@ -940,7 +941,7 @@
           <t>1人1月あたり給付費の実績値の年度</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>［要協議］令和7年度を選ぶ案</t>
         </is>
@@ -953,7 +954,7 @@
       <c r="E26" s="6" t="inlineStr"/>
     </row>
     <row r="28" ht="14" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>注）本節の①から⑤までは、弊社の別案件において実際に小数を入力して出力された推計結果により確かめたものです。その保険者の数値は用いていません。</t>
         </is>
@@ -1387,7 +1388,7 @@
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>注1）★の行が入力値です。
 注2）画面が性別・年齢階級別の入力を求める場合は、年齢階級別は上表のとおりです。性別は男 602人・女 1,382人で、年齢階級との組合せも年報（様式1の5）にあります。
@@ -2047,7 +2048,7 @@
       </c>
     </row>
     <row r="21" ht="56" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>注1）人数の欄は整数で扱われるため、下段の「（整数）」が入力値です（00シート3参照）。上段の★の行は年報の値を12で除したそのままの値で、整数版はこれを群（要支援・要介護）ごとに合計を保って丸めたものです。
 注2）施設・居住系の計は480.167人です。画面の令和8年度（4か月）は474人、画面の令和7年度は482人です。
@@ -2253,7 +2254,7 @@
       </c>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>注1）本表の入力値は年報の実数であり、この分母を用いた按分によるものではありません。上表は、画面に表示される在宅サービス利用率（利用者数÷在宅の認定者数）を読むために掲げています。素案の令和8年度の値を同年度の利用率で割ると50人以上のサービスでいずれも1,500人前後になり、分母が共通であることを確かめています。</t>
         </is>
@@ -3471,7 +3472,7 @@
       </c>
     </row>
     <row r="49" ht="56" customHeight="1">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>注2）人数の欄は整数で扱われるため、下段の「（整数）」が入力値です（00シート3参照）。
 注3）整数に丸めると計が0又は1になるサービスが2件あります（定期巡回・随時対応型訪問介護看護・認知症対応型通所介護）。群ごとに合計を保つ丸め方によるため、定期巡回・随時対応型訪問介護看護（月0.583人）は要介護5に1人が立ち、0にはなりません。各欄を単純に四捨五入すると全欄が0になり、令和9年度から令和11年度も0のまま残ります。
@@ -4553,7 +4554,7 @@
       <c r="K34" s="6" t="inlineStr"/>
     </row>
     <row r="36" ht="42" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>注1）★の行（小数第1位）が入力値です。利用回（日）数の欄は小数第1位まで受け付けます（05シート1参照）。丸めは群（要支援・要介護）ごとに合計を保つ最大剰余法によります。上段の「（実数）」は年報の値を12で除したそのままの値です。下段の「（2区分）」は、要支援1の位置に要支援計、要介護3の位置に要介護計を置いたものです。
 注2）要支援の欄が0のサービスは、予防給付が総合事業へ移行したもの（訪問介護・通所介護）、予防給付の区分がないもの（地域密着型通所介護・認知症対応型通所介護は要支援の実績が0）、月を単位とする報酬で回（日）数を持たないもの（介護予防通所リハビリテーションは受給者83人／月に対し利用回数が0）です。
@@ -4661,7 +4662,7 @@
           <t>すべて整数</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>整数版（02・03シートの下段）</t>
         </is>
@@ -4691,14 +4692,14 @@
           <t>小数第1位まで</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>小数第1位版（04シートの★の行）</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>注1）弊社の別案件において、令和8年度の実績見込み値を編集し小数を入力したうえで出力された推計結果により確かめたものです。同じ表の中で令和6・7年度の人数は小数10桁まで表示されるのに対し、編集した令和8年度の人数は全45サービスが整数、令和9年度から令和11年度の人数も全135件が整数でした。利用回（日）数は令和8年度・令和9年度以降とも小数第1位まで出ています。その保険者の数値は用いていません。
 注2）したがって、人数については「小数で入力できるか」ではなく「整数に丸めたときに小口が消えないか」が論点になります。本表の整数版は群（要支援・要介護）ごとに合計を保つため、定期巡回・随時対応型訪問介護看護は要介護5に1人が立ちます。</t>
@@ -4758,7 +4759,7 @@
           <t>+4.1%</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>一致（61.500）</t>
         </is>
@@ -4782,7 +4783,7 @@
           <t>+0.5%</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>一致（81.583）</t>
         </is>
@@ -4806,7 +4807,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>一致（0.000）</t>
         </is>
@@ -4830,7 +4831,7 @@
           <t>+1.3%</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>一致（59.250）</t>
         </is>
@@ -4854,7 +4855,7 @@
           <t>+1.3%</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>一致（138.250）</t>
         </is>
@@ -4878,7 +4879,7 @@
           <t>-3.0%</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>一致（134.083）</t>
         </is>
@@ -4902,14 +4903,14 @@
           <t>+9.1%</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>一致（5.500）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>注1）画面の整数と2％以上の差があるのは3件（特定施設入居者生活介護・介護老人保健施設・介護医療院）です。
 注2）年報の要介護度別を12で除した月平均は総括表詳細（１）の令和7年度と一致します。総括表詳細（１）の利用者数に総括表詳細（４）の1人1月あたり給付費を乗じると総括表詳細（５）の給付費になり、その合計は年報の給付費と円単位で一致します（令和7年度 2,915,307,125円）。年報・総括表・給付費が一つの系列でつながっています。
@@ -4965,7 +4966,7 @@
       <c r="D25" s="16" t="n">
         <v>270.083</v>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
@@ -4989,7 +4990,7 @@
       <c r="D26" s="16" t="n">
         <v>5.25</v>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
@@ -5013,7 +5014,7 @@
       <c r="D27" s="16" t="n">
         <v>135.167</v>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
@@ -5037,7 +5038,7 @@
       <c r="D28" s="16" t="n">
         <v>66.917</v>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
@@ -5061,7 +5062,7 @@
       <c r="D29" s="16" t="n">
         <v>193.25</v>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
@@ -5085,7 +5086,7 @@
       <c r="D30" s="16" t="n">
         <v>97.333</v>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
@@ -5109,7 +5110,7 @@
       <c r="D31" s="16" t="n">
         <v>273.25</v>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
@@ -5133,7 +5134,7 @@
       <c r="D32" s="16" t="n">
         <v>26.5</v>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
@@ -5157,7 +5158,7 @@
       <c r="D33" s="16" t="n">
         <v>16.583</v>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
@@ -5181,7 +5182,7 @@
       <c r="D34" s="16" t="n">
         <v>642.083</v>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
@@ -5205,7 +5206,7 @@
       <c r="D35" s="16" t="n">
         <v>10.75</v>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
@@ -5229,7 +5230,7 @@
       <c r="D36" s="16" t="n">
         <v>8.417</v>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
@@ -5253,7 +5254,7 @@
       <c r="D37" s="16" t="n">
         <v>913.333</v>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
@@ -5277,7 +5278,7 @@
       <c r="D38" s="16" t="n">
         <v>0.583</v>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
@@ -5301,7 +5302,7 @@
       <c r="D39" s="16" t="n">
         <v>76.167</v>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
@@ -5325,7 +5326,7 @@
       <c r="D40" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E40" s="8" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
@@ -5349,7 +5350,7 @@
       <c r="D41" s="16" t="n">
         <v>99.917</v>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
@@ -5568,7 +5569,7 @@
           <t>1984人／年報の第1号合計1984人</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5594,7 +5595,7 @@
           <t>全件一致</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5620,7 +5621,7 @@
           <t>全件一致</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5646,7 +5647,7 @@
           <t>保っている</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5672,7 +5673,7 @@
           <t>1503.8人</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5698,7 +5699,7 @@
           <t>年報÷12 270.08人（差-1.0%）</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5724,7 +5725,7 @@
           <t>令和7年度 2,915,307,125円（年報と一致）</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5750,7 +5751,7 @@
           <t>2件：定期巡回・随時対応型訪問介護看護・認知症対応型通所介護</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5776,7 +5777,7 @@
           <t>3件：特定施設入居者生活介護・介護老人保健施設・介護医療院</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5802,7 +5803,7 @@
           <t>10サービス。要支援・要介護の2区分の計も併記</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5828,7 +5829,7 @@
           <t>全件一致</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5854,7 +5855,7 @@
           <t>実績のある欄はない</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5880,7 +5881,7 @@
           <t>介護老人保健施設に年間の延べ15人（第1号1,594＋第2号15＝1,609）。02シート注4に記載</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5906,7 +5907,7 @@
           <t>消えるものはない（定期巡回は月0.583人で要介護5に1人が立つ）</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5932,7 +5933,7 @@
           <t>全件0.05以内</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5964,7 +5965,7 @@
       <c r="F20" s="11" t="inlineStr"/>
     </row>
     <row r="22" ht="56" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>注1）点検2・3が本表の要です。年報の要介護度別を12で除して足した値が、見える化システムの総括表詳細（１）の令和7年度と施設・居住系7サービス・在宅17サービスのすべてで一致します（許容0.0005人）。年報と総括表が同じ系列であることが確かめられ、要介護度別の内訳を確定値として扱えます。
 注2）点検11は、④を③で除して1人1月あたりに戻したとき総括表詳細（３）と一致するかの点検です。④と③が同じ集計から出ていることを確かめています。
@@ -5989,7 +5990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6123,7 +6124,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の令和7年度について、画面に表示された値と年報の要介護度別を12で除した値が一致しない。特定施設入居者生活介護は画面64人・年報61.50人（＋4.1％）、介護老人保健施設は画面130人・年報134.08人（▲3.0％）、介護医療院は画面6人・年報5.50人（＋9.1％）である。年報の側は、要介護度別の和÷12が総括表詳細（１）と全24サービスで一致し、総括表の給付費の合計が年報の給付費と円単位で一致する（令和7年度 2,915,307,125円）。画面の整数がどのように作られているかを当方は確かめられていない。①画面の値の作り方をご確認いただきたい（保険者単位と3町合計の違い、時点の違い、現物給付分と償還払いを含む件数の違いのいずれか）。②本表は年報の値を用いる整理としてよいかご判断いただきたい。③画面の令和7年度は要介護度別の和と合計欄が1人ずれる行があり（特定施設63対64、介護老人福祉施設141対140）、画面の値をそのまま貼ると誤差が入る。</t>
+          <t>施設・居住系の令和7年度について、画面に表示された値と年報の要介護度別を12で除した値が一致しない。特定施設入居者生活介護は画面64人・年報61.50人（＋4.1％）、介護老人保健施設は画面130人・年報134.08人（▲3.0％）、介護医療院は画面6人・年報5.50人（＋9.1％）である。年報の側は、要介護度別の和÷12が総括表詳細（１）と全24サービスで一致し、総括表の給付費の合計が年報の給付費と円単位で一致する（令和7年度 2,915,307,125円）。画面の整数がどのように作られているかを当方は確かめられていない。①画面の値の作り方をご確認いただきたい（保険者単位と3町合計の違い、時点の違い、現物給付分と償還払いを含む件数の違いのいずれか）。なお受領した画面の写しには「介護保険事業状況報告の設定」の初期値が「令和6年度年報及び令和7年度、8年度の最新の月報」と記されている。画面の令和7年度が年報ではなく月報によるものであれば食い違いの説明になる。当方は月報（令和7年度）を保有していないため確かめられていない。②本表は年報の値を用いる整理としてよいかご判断いただきたい。③画面の令和7年度は要介護度別の和と合計欄が1人ずれる行があり（特定施設63対64、介護老人福祉施設141対140）、画面の値をそのまま貼ると誤差が入る。</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -6176,10 +6177,42 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>注1）本表に係る確認事項は4件（No.134〜No.137）で、うちNo.134は取下げ、No.135は解決しました。ご判断・ご確認をお願いするのはNo.136・No.137の2件です。
+    <row r="9" ht="150" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>No.138</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>当方は令和8年9月11日に「差し替えは4画面ある」とお伝えしたが、①認定者数について編集する項目が画面にあるかを確かめられていない。①受領した画面の写しで「実績及び推計方法の設定」に列挙されている編集項目は、（3）1）施設・居住系サービス利用者数の実績見込み値、（4）1）在宅サービス利用者数の実績見込み値、（4）2）在宅サービス利用回（日）数の実績見込み値の3件であり、認定者数の実績見込み値を編集する項目は写っていない。②画面の認定率は令和7年度・令和8年度とも20.84％で同じであり、令和8年度は既に令和7年度の率で置かれている可能性がある。③編集する項目がある場合は01シートの実数（1,984人）を入力する。ただし見える化システムの認定率の定義は当方と異なるため（画面20.84％・当方21.8％。時点も画面は各年9月末、当方は年度末。確認事項No.125が未解決）、年度末の実数をそのまま置いてよいかを併せてご確認いただきたい。④編集する項目がない場合は、認定率の伸びに「当該市町村における令和6年度→令和7年度の伸び」を選ぶことで令和8年度の影響を避ける形になる。</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>将来推計 第2段階</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>注1）本表に係る確認事項は5件（No.134〜No.138）で、うちNo.134は取下げ、No.135は解決しました。ご判断・ご確認をお願いするのはNo.136・No.137・No.138の3件です。このうちNo.138（認定者数の編集項目の有無）は入力を始める前にご確認いただく必要があります。
 注2）既に起票済みのNo.128（実績見込み値を編集するか）・No.132（在宅の編集画面の現在値）・No.133（介護老人保健施設の減少）とも関わります。No.132（在宅の編集画面の現在値のご提供）は、年報により入力値が確定したため、画面の並びに合わせるための参考にとどまります。
 注3）確認事項は業務工程管理表 03_確認事項一覧で一元管理します。</t>
         </is>
@@ -6188,8 +6221,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
